--- a/docs/상세개발계획서 AI담당.xlsx
+++ b/docs/상세개발계획서 AI담당.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sungjonghyun/3-1/산학프로젝트/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sungjonghyun/3-1/산학프로젝트/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88467AA7-C7D4-634B-B565-FCCEAC28D635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2C4BF4-F5DC-0844-A25A-91EC00E46BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="61">
   <si>
     <t>Task</t>
   </si>
@@ -341,10 +341,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>vlm 통합 모델 고려</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>냉장고 전체인식
 → YOLO, vlm</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -355,6 +351,117 @@
   </si>
   <si>
     <t>정확도에 대한 기준 데이터셋 정의 후 성능 테스트</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>VLM 하이브리드 통합 모델</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동라벨링(미인식 데이터 자동 라벨링 파이프라인 구축)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>타 파트 연동 준비(백엔드 연동용 추론 결과 반환 규격)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 디렉터리 전면 개편 및 Git 연동 세팅</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Git 연동 세팅</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>FastAPI 서버 구축</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신뢰도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 75%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미만 시 VLM(Gemini) 추론 연동</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Self-improving </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기반</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ngrok </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">외부접속 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, bearer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>토큰 인증</t>
+    </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1264,19 +1371,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFFFFFFF"/>
       </left>
@@ -1287,6 +1381,19 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1411,10 +1518,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1423,11 +1527,74 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1440,18 +1607,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1486,6 +1641,9 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1501,59 +1659,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1775,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z996"/>
+  <dimension ref="A1:AA999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -1786,13 +1893,13 @@
     <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="12" width="5.83203125" bestFit="1" customWidth="1"/>
     <col min="13" max="19" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.5" customWidth="1"/>
+    <col min="20" max="20" width="40.1640625" customWidth="1"/>
     <col min="21" max="22" width="5.1640625" customWidth="1"/>
     <col min="23" max="23" width="9.33203125" customWidth="1"/>
     <col min="24" max="26" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="16.5" customHeight="1">
+    <row r="1" spans="1:27" ht="16.5" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1820,28 +1927,28 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="42.75" customHeight="1">
+    <row r="2" spans="1:27" ht="42.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="49"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="44"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -1850,26 +1957,26 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="42.75" customHeight="1">
+    <row r="3" spans="1:27" ht="42.75" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="52"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="47"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -1878,26 +1985,26 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="16.5" customHeight="1" thickBot="1">
+    <row r="4" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1906,16 +2013,16 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="29.25" customHeight="1">
+    <row r="5" spans="1:27" ht="29.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="75" t="s">
+      <c r="C5" s="44"/>
+      <c r="D5" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="78" t="s">
+      <c r="E5" s="56" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1924,25 +2031,25 @@
       <c r="G5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="66" t="s">
+      <c r="H5" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="81" t="s">
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="81" t="s">
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="82"/>
-      <c r="S5" s="83"/>
-      <c r="T5" s="43" t="s">
+      <c r="R5" s="60"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="64" t="s">
         <v>8</v>
       </c>
       <c r="U5" s="1"/>
@@ -1952,12 +2059,12 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="29.25" customHeight="1">
+    <row r="6" spans="1:27" ht="29.25" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="79"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="57"/>
       <c r="F6" s="3" t="s">
         <v>9</v>
       </c>
@@ -2000,23 +2107,25 @@
       <c r="S6" s="27">
         <v>17</v>
       </c>
-      <c r="T6" s="44"/>
+      <c r="T6" s="52"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
-    </row>
-    <row r="7" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+      <c r="Z6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="80"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="58"/>
       <c r="F7" s="7" t="s">
         <v>12</v>
       </c>
@@ -2059,29 +2168,31 @@
       <c r="S7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="T7" s="44"/>
+      <c r="T7" s="52"/>
       <c r="U7" s="1"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
-    </row>
-    <row r="8" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="49"/>
+      <c r="C8" s="44"/>
       <c r="D8" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="63"/>
-      <c r="G8" s="56"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="72"/>
       <c r="H8" s="36" t="s">
         <v>10</v>
       </c>
@@ -2090,14 +2201,14 @@
       <c r="K8" s="20"/>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
-      <c r="N8" s="64" t="s">
+      <c r="N8" s="81" t="s">
         <v>27</v>
       </c>
       <c r="O8" s="21"/>
       <c r="P8" s="21"/>
       <c r="Q8" s="21"/>
       <c r="R8" s="21"/>
-      <c r="S8" s="45" t="s">
+      <c r="S8" s="65" t="s">
         <v>28</v>
       </c>
       <c r="T8" s="11"/>
@@ -2107,18 +2218,18 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="9" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="44"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="60"/>
-      <c r="G9" s="57"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="73"/>
       <c r="H9" s="36" t="s">
         <v>10</v>
       </c>
@@ -2127,12 +2238,12 @@
       <c r="K9" s="20"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
-      <c r="N9" s="46"/>
+      <c r="N9" s="66"/>
       <c r="O9" s="19"/>
       <c r="P9" s="19"/>
       <c r="Q9" s="19"/>
       <c r="R9" s="19"/>
-      <c r="S9" s="46"/>
+      <c r="S9" s="66"/>
       <c r="T9" s="11"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -2140,18 +2251,18 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="10" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="44"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="52"/>
       <c r="D10" s="12" t="s">
         <v>44</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="60"/>
-      <c r="G10" s="57"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="73"/>
       <c r="H10" s="36" t="s">
         <v>10</v>
       </c>
@@ -2162,111 +2273,122 @@
       <c r="K10" s="20"/>
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
-      <c r="N10" s="46"/>
+      <c r="N10" s="66"/>
       <c r="O10" s="19"/>
       <c r="P10" s="19"/>
       <c r="Q10" s="19"/>
       <c r="R10" s="19"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="1"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="11" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="44"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="52"/>
       <c r="D11" s="12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="60"/>
-      <c r="G11" s="57"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="73"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="6" t="s">
+        <v>10</v>
+      </c>
       <c r="M11" s="19"/>
-      <c r="N11" s="46"/>
+      <c r="N11" s="66"/>
       <c r="O11" s="19"/>
       <c r="P11" s="19"/>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="11"/>
+      <c r="S11" s="66"/>
+      <c r="T11" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="12" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="79"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="13" t="s">
-        <v>34</v>
+      <c r="B12" s="57"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="86" t="s">
+        <v>52</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="86"/>
-      <c r="G12" s="57"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="73"/>
       <c r="H12" s="19"/>
-      <c r="I12" s="36" t="s">
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="K12" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="19"/>
       <c r="M12" s="19"/>
-      <c r="N12" s="46"/>
+      <c r="N12" s="66"/>
       <c r="O12" s="19"/>
       <c r="P12" s="19"/>
       <c r="Q12" s="19"/>
       <c r="R12" s="19"/>
-      <c r="S12" s="46"/>
-      <c r="T12" s="11"/>
+      <c r="S12" s="66"/>
+      <c r="T12" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="13" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="51"/>
+      <c r="B13" s="57"/>
       <c r="C13" s="52"/>
       <c r="D13" s="13" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="61"/>
-      <c r="G13" s="58"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="73"/>
       <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="46"/>
+      <c r="I13" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N13" s="66"/>
       <c r="O13" s="19"/>
       <c r="P13" s="19"/>
       <c r="Q13" s="19"/>
       <c r="R13" s="19"/>
-      <c r="S13" s="46"/>
+      <c r="S13" s="66"/>
       <c r="T13" s="11"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -2274,34 +2396,32 @@
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="14" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="9" t="s">
-        <v>42</v>
+      <c r="B14" s="57"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="13" t="s">
+        <v>53</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="63"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="36" t="s">
+      <c r="F14" s="80"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="21"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="46"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="66"/>
       <c r="O14" s="19"/>
       <c r="P14" s="19"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="19"/>
-      <c r="S14" s="46"/>
+      <c r="S14" s="66"/>
       <c r="T14" s="11"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
@@ -2309,32 +2429,34 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="15" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="9" t="s">
-        <v>35</v>
+      <c r="B15" s="57"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="60"/>
-      <c r="G15" s="57"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="73"/>
       <c r="H15" s="19"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="36" t="s">
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="20"/>
-      <c r="L15" s="19"/>
+      <c r="L15" s="36" t="s">
+        <v>10</v>
+      </c>
       <c r="M15" s="19"/>
-      <c r="N15" s="46"/>
+      <c r="N15" s="66"/>
       <c r="O15" s="19"/>
       <c r="P15" s="19"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
-      <c r="S15" s="46"/>
+      <c r="S15" s="66"/>
       <c r="T15" s="11"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
@@ -2342,32 +2464,30 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="16" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="12" t="s">
-        <v>41</v>
+      <c r="B16" s="45"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="60"/>
-      <c r="G16" s="57"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="74"/>
       <c r="H16" s="19"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K16" s="20"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
       <c r="L16" s="19"/>
       <c r="M16" s="19"/>
-      <c r="N16" s="46"/>
+      <c r="N16" s="66"/>
       <c r="O16" s="19"/>
       <c r="P16" s="19"/>
       <c r="Q16" s="19"/>
       <c r="R16" s="19"/>
-      <c r="S16" s="46"/>
+      <c r="S16" s="66"/>
       <c r="T16" s="11"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
@@ -2375,30 +2495,34 @@
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="17" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="50"/>
+      <c r="B17" s="69" t="s">
+        <v>32</v>
+      </c>
       <c r="C17" s="44"/>
-      <c r="D17" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="6" t="s">
+      <c r="D17" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="79"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="20"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="46"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="66"/>
       <c r="O17" s="19"/>
       <c r="P17" s="19"/>
       <c r="Q17" s="19"/>
       <c r="R17" s="19"/>
-      <c r="S17" s="46"/>
+      <c r="S17" s="66"/>
       <c r="T17" s="11"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
@@ -2406,26 +2530,32 @@
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="18" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A18" s="1"/>
       <c r="B18" s="51"/>
       <c r="C18" s="52"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="58"/>
+      <c r="D18" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="76"/>
+      <c r="G18" s="73"/>
       <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="36" t="s">
+        <v>10</v>
+      </c>
       <c r="K18" s="20"/>
       <c r="L18" s="19"/>
       <c r="M18" s="19"/>
-      <c r="N18" s="46"/>
+      <c r="N18" s="66"/>
       <c r="O18" s="19"/>
       <c r="P18" s="19"/>
       <c r="Q18" s="19"/>
       <c r="R18" s="19"/>
-      <c r="S18" s="46"/>
+      <c r="S18" s="66"/>
       <c r="T18" s="11"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
@@ -2433,66 +2563,65 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="19" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="54" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="14" t="s">
-        <v>39</v>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="59"/>
-      <c r="G19" s="62"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="73"/>
       <c r="H19" s="19"/>
-      <c r="I19" s="36" t="s">
+      <c r="I19" s="39"/>
+      <c r="J19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J19" s="19"/>
       <c r="K19" s="20"/>
       <c r="L19" s="19"/>
       <c r="M19" s="19"/>
-      <c r="N19" s="46"/>
+      <c r="N19" s="66"/>
       <c r="O19" s="19"/>
       <c r="P19" s="19"/>
       <c r="Q19" s="19"/>
       <c r="R19" s="19"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="42" t="s">
-        <v>47</v>
-      </c>
+      <c r="S19" s="66"/>
+      <c r="T19" s="11"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="20" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="44"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="60"/>
-      <c r="G20" s="57"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="73"/>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
+      <c r="J20" s="6" t="s">
+        <v>10</v>
+      </c>
       <c r="K20" s="20"/>
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
-      <c r="N20" s="46"/>
+      <c r="N20" s="66"/>
       <c r="O20" s="19"/>
       <c r="P20" s="19"/>
       <c r="Q20" s="19"/>
       <c r="R20" s="19"/>
-      <c r="S20" s="46"/>
+      <c r="S20" s="66"/>
       <c r="T20" s="11"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -2500,26 +2629,32 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="21" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="57"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="77"/>
+      <c r="G21" s="74"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
       <c r="J21" s="19"/>
       <c r="K21" s="20"/>
       <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="46"/>
+      <c r="M21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N21" s="66"/>
       <c r="O21" s="19"/>
       <c r="P21" s="19"/>
       <c r="Q21" s="19"/>
       <c r="R21" s="19"/>
-      <c r="S21" s="46"/>
+      <c r="S21" s="66"/>
       <c r="T21" s="11"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -2527,55 +2662,66 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="22" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="50"/>
+      <c r="B22" s="70" t="s">
+        <v>48</v>
+      </c>
       <c r="C22" s="44"/>
-      <c r="D22" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="57"/>
+      <c r="D22" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="75"/>
+      <c r="G22" s="78"/>
       <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
+      <c r="I22" s="36" t="s">
+        <v>10</v>
+      </c>
       <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="40"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="19"/>
       <c r="M22" s="19"/>
-      <c r="N22" s="46"/>
+      <c r="N22" s="66"/>
       <c r="O22" s="19"/>
       <c r="P22" s="19"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="19"/>
-      <c r="S22" s="46"/>
-      <c r="T22" s="11"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="41" t="s">
+        <v>47</v>
+      </c>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="23" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="57"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="76"/>
+      <c r="G23" s="73"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
       <c r="K23" s="20"/>
       <c r="L23" s="19"/>
       <c r="M23" s="19"/>
-      <c r="N23" s="46"/>
+      <c r="N23" s="66"/>
       <c r="O23" s="19"/>
       <c r="P23" s="19"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
-      <c r="S23" s="46"/>
+      <c r="S23" s="66"/>
       <c r="T23" s="11"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
@@ -2583,25 +2729,26 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="24" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A24" s="1"/>
       <c r="B24" s="51"/>
       <c r="C24" s="52"/>
-      <c r="D24" s="13"/>
+      <c r="D24" s="12"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="58"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="73"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
       <c r="K24" s="20"/>
       <c r="L24" s="19"/>
       <c r="M24" s="19"/>
-      <c r="N24" s="46"/>
+      <c r="N24" s="66"/>
       <c r="O24" s="19"/>
       <c r="P24" s="19"/>
       <c r="Q24" s="19"/>
       <c r="R24" s="19"/>
-      <c r="S24" s="46"/>
+      <c r="S24" s="66"/>
       <c r="T24" s="11"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
@@ -2609,32 +2756,30 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="25" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="49"/>
-      <c r="D25" s="14" t="s">
-        <v>45</v>
+      <c r="B25" s="51"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="59"/>
-      <c r="G25" s="62"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="73"/>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
       <c r="J25" s="19"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="39"/>
       <c r="M25" s="19"/>
-      <c r="N25" s="46"/>
+      <c r="N25" s="66"/>
       <c r="O25" s="19"/>
       <c r="P25" s="19"/>
       <c r="Q25" s="19"/>
       <c r="R25" s="19"/>
-      <c r="S25" s="46"/>
+      <c r="S25" s="66"/>
       <c r="T25" s="11"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
@@ -2642,30 +2787,26 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="26" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="60"/>
-      <c r="G26" s="57"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="73"/>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="20"/>
       <c r="L26" s="19"/>
       <c r="M26" s="19"/>
-      <c r="N26" s="46"/>
+      <c r="N26" s="66"/>
       <c r="O26" s="19"/>
       <c r="P26" s="19"/>
       <c r="Q26" s="19"/>
       <c r="R26" s="19"/>
-      <c r="S26" s="46"/>
+      <c r="S26" s="66"/>
       <c r="T26" s="11"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
@@ -2673,30 +2814,25 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="27" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="60"/>
-      <c r="G27" s="57"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="74"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
       <c r="K27" s="20"/>
       <c r="L27" s="19"/>
       <c r="M27" s="19"/>
-      <c r="N27" s="46"/>
+      <c r="N27" s="66"/>
       <c r="O27" s="19"/>
       <c r="P27" s="19"/>
       <c r="Q27" s="19"/>
       <c r="R27" s="19"/>
-      <c r="S27" s="46"/>
+      <c r="S27" s="66"/>
       <c r="T27" s="11"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
@@ -2704,181 +2840,204 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="28" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="50"/>
+      <c r="B28" s="71" t="s">
+        <v>36</v>
+      </c>
       <c r="C28" s="44"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="57"/>
+      <c r="D28" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="75"/>
+      <c r="G28" s="78"/>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
       <c r="K28" s="20"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="46"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N28" s="66"/>
       <c r="O28" s="19"/>
       <c r="P28" s="19"/>
       <c r="Q28" s="19"/>
       <c r="R28" s="19"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="11"/>
+      <c r="S28" s="66"/>
+      <c r="T28" s="11" t="s">
+        <v>60</v>
+      </c>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="29" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="44"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="57"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="76"/>
+      <c r="G29" s="73"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
+      <c r="J29" s="20"/>
       <c r="K29" s="20"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="46"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N29" s="66"/>
       <c r="O29" s="19"/>
       <c r="P29" s="19"/>
       <c r="Q29" s="19"/>
       <c r="R29" s="19"/>
-      <c r="S29" s="46"/>
-      <c r="T29" s="11"/>
+      <c r="S29" s="66"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
+    <row r="30" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A30" s="1"/>
       <c r="B30" s="51"/>
       <c r="C30" s="52"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="58"/>
+      <c r="D30" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="76"/>
+      <c r="G30" s="73"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="65"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N30" s="66"/>
       <c r="O30" s="19"/>
       <c r="P30" s="19"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="19"/>
-      <c r="S30" s="47"/>
-      <c r="T30" s="15"/>
+      <c r="S30" s="66"/>
+      <c r="T30" s="11"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="16.5" customHeight="1">
+    <row r="31" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="38"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="76"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="66"/>
+      <c r="T31" s="11"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
-    </row>
-    <row r="32" spans="1:26" ht="16.5" customHeight="1">
+    </row>
+    <row r="32" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="66"/>
+      <c r="T32" s="11"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-    </row>
-    <row r="33" spans="1:26" ht="16.5" customHeight="1">
+    </row>
+    <row r="33" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="74"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="82"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="67"/>
+      <c r="T33" s="15"/>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
-      <c r="Z33" s="1"/>
     </row>
     <row r="34" spans="1:26" ht="16.5" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
-      <c r="C34" s="16"/>
+      <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
+      <c r="K34" s="38"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -2898,7 +3057,7 @@
     <row r="35" spans="1:26" ht="16.5" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="16"/>
+      <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -2982,7 +3141,7 @@
     <row r="38" spans="1:26" ht="16.5" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
+      <c r="C38" s="16"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -3010,7 +3169,7 @@
     <row r="39" spans="1:26" ht="16.5" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
+      <c r="C39" s="16"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -3038,9 +3197,9 @@
     <row r="40" spans="1:26" ht="16.5" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -3067,8 +3226,8 @@
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -3095,8 +3254,8 @@
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -3207,8 +3366,8 @@
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -3235,8 +3394,8 @@
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -3263,8 +3422,8 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -8383,9 +8542,90 @@
       <c r="Y230" s="1"/>
       <c r="Z230" s="1"/>
     </row>
-    <row r="231" spans="1:26" ht="15.75" customHeight="1"/>
-    <row r="232" spans="1:26" ht="15.75" customHeight="1"/>
-    <row r="233" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="231" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A231" s="1"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
+      <c r="E231" s="1"/>
+      <c r="F231" s="1"/>
+      <c r="G231" s="1"/>
+      <c r="H231" s="1"/>
+      <c r="I231" s="1"/>
+      <c r="J231" s="1"/>
+      <c r="K231" s="1"/>
+      <c r="L231" s="1"/>
+      <c r="M231" s="1"/>
+      <c r="N231" s="1"/>
+      <c r="O231" s="1"/>
+      <c r="P231" s="1"/>
+      <c r="Q231" s="1"/>
+      <c r="R231" s="1"/>
+      <c r="S231" s="1"/>
+      <c r="T231" s="1"/>
+      <c r="U231" s="1"/>
+      <c r="V231" s="1"/>
+      <c r="W231" s="1"/>
+      <c r="X231" s="1"/>
+      <c r="Y231" s="1"/>
+      <c r="Z231" s="1"/>
+    </row>
+    <row r="232" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A232" s="1"/>
+      <c r="B232" s="1"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
+      <c r="E232" s="1"/>
+      <c r="F232" s="1"/>
+      <c r="G232" s="1"/>
+      <c r="H232" s="1"/>
+      <c r="I232" s="1"/>
+      <c r="J232" s="1"/>
+      <c r="K232" s="1"/>
+      <c r="L232" s="1"/>
+      <c r="M232" s="1"/>
+      <c r="N232" s="1"/>
+      <c r="O232" s="1"/>
+      <c r="P232" s="1"/>
+      <c r="Q232" s="1"/>
+      <c r="R232" s="1"/>
+      <c r="S232" s="1"/>
+      <c r="T232" s="1"/>
+      <c r="U232" s="1"/>
+      <c r="V232" s="1"/>
+      <c r="W232" s="1"/>
+      <c r="X232" s="1"/>
+      <c r="Y232" s="1"/>
+      <c r="Z232" s="1"/>
+    </row>
+    <row r="233" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A233" s="1"/>
+      <c r="B233" s="1"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
+      <c r="E233" s="1"/>
+      <c r="F233" s="1"/>
+      <c r="G233" s="1"/>
+      <c r="H233" s="1"/>
+      <c r="I233" s="1"/>
+      <c r="J233" s="1"/>
+      <c r="K233" s="1"/>
+      <c r="L233" s="1"/>
+      <c r="M233" s="1"/>
+      <c r="N233" s="1"/>
+      <c r="O233" s="1"/>
+      <c r="P233" s="1"/>
+      <c r="Q233" s="1"/>
+      <c r="R233" s="1"/>
+      <c r="S233" s="1"/>
+      <c r="T233" s="1"/>
+      <c r="U233" s="1"/>
+      <c r="V233" s="1"/>
+      <c r="W233" s="1"/>
+      <c r="X233" s="1"/>
+      <c r="Y233" s="1"/>
+      <c r="Z233" s="1"/>
+    </row>
     <row r="234" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="235" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="236" spans="1:26" ht="15.75" customHeight="1"/>
@@ -9149,8 +9389,27 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="T5:T7"/>
+    <mergeCell ref="S8:S33"/>
+    <mergeCell ref="B8:C16"/>
+    <mergeCell ref="B17:C21"/>
+    <mergeCell ref="B22:C27"/>
+    <mergeCell ref="B28:C33"/>
+    <mergeCell ref="G8:G16"/>
+    <mergeCell ref="F22:F27"/>
+    <mergeCell ref="G22:G27"/>
+    <mergeCell ref="F28:F33"/>
+    <mergeCell ref="G28:G33"/>
+    <mergeCell ref="F8:F16"/>
+    <mergeCell ref="N8:N33"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="G17:G21"/>
     <mergeCell ref="B2:S3"/>
     <mergeCell ref="B4:S4"/>
     <mergeCell ref="B5:C7"/>
@@ -9158,22 +9417,6 @@
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="Q5:S5"/>
     <mergeCell ref="M5:P5"/>
-    <mergeCell ref="T5:T7"/>
-    <mergeCell ref="S8:S30"/>
-    <mergeCell ref="B8:C13"/>
-    <mergeCell ref="B14:C18"/>
-    <mergeCell ref="B19:C24"/>
-    <mergeCell ref="B25:C30"/>
-    <mergeCell ref="G8:G13"/>
-    <mergeCell ref="F19:F24"/>
-    <mergeCell ref="G19:G24"/>
-    <mergeCell ref="F25:F30"/>
-    <mergeCell ref="G25:G30"/>
-    <mergeCell ref="F8:F13"/>
-    <mergeCell ref="N8:N30"/>
-    <mergeCell ref="F14:F18"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="G14:G18"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/docs/상세개발계획서 AI담당.xlsx
+++ b/docs/상세개발계획서 AI담당.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sungjonghyun/3-1/산학프로젝트/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2C4BF4-F5DC-0844-A25A-91EC00E46BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCC2A18-6FB9-E949-A222-9368238470C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="67">
   <si>
     <t>Task</t>
   </si>
@@ -101,14 +101,6 @@
   </si>
   <si>
     <t>미 진행</t>
-  </si>
-  <si>
-    <t xml:space="preserve">중
-간
-발
-표
-</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">최
@@ -254,10 +246,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>YOLO 모델 완료 후 연동</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>기본 YOLO 성능 테스트</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -338,11 +326,6 @@
       </rPr>
       <t>부족</t>
     </r>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉장고 전체인식
-→ YOLO, vlm</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -464,12 +447,49 @@
     </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
+  <si>
+    <t>냉장고 전체인식
+→ Gemini Vision</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉장고 물체 감지 — Gemini Vision 구현</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉장고 전체인식 모델 완료 후 연동</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>인프라 &lt;-&gt; AI 연동</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>서버 사용자 로깅 추가</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gemini API 타임아웃 설정</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>한계점:학습/검증 데이터와 독립된 테스트셋 구축 어려움 존재, 추후 실환경 데이터 수집을 통한 별도 평가 예정</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>60개 클래스 학습 완료 모델(ver3)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>최종 Val Acc: 94.73% (Epoch 17)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -582,6 +602,20 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -651,7 +685,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="62">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -1084,15 +1118,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1400,7 +1425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1464,11 +1489,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1479,7 +1507,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1506,19 +1534,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1527,74 +1552,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1607,6 +1572,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1644,11 +1624,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1656,10 +1633,61 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1882,7 +1910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA999"/>
+  <dimension ref="A1:AA1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -1893,7 +1921,7 @@
     <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="12" width="5.83203125" bestFit="1" customWidth="1"/>
     <col min="13" max="19" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="40.1640625" customWidth="1"/>
+    <col min="20" max="20" width="77.33203125" customWidth="1"/>
     <col min="21" max="22" width="5.1640625" customWidth="1"/>
     <col min="23" max="23" width="9.33203125" customWidth="1"/>
     <col min="24" max="26" width="5" customWidth="1"/>
@@ -1929,26 +1957,26 @@
     </row>
     <row r="2" spans="1:27" ht="42.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="44"/>
+      <c r="B2" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="49"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -1959,24 +1987,24 @@
     </row>
     <row r="3" spans="1:27" ht="42.75" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="47"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="53"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -1987,24 +2015,24 @@
     </row>
     <row r="4" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="49"/>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="49"/>
-      <c r="S4" s="49"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -2015,14 +2043,14 @@
     </row>
     <row r="5" spans="1:27" ht="29.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="53" t="s">
+      <c r="C5" s="49"/>
+      <c r="D5" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="E5" s="78" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -2031,25 +2059,25 @@
       <c r="G5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="83" t="s">
+      <c r="H5" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="59" t="s">
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="59" t="s">
+      <c r="N5" s="83"/>
+      <c r="O5" s="83"/>
+      <c r="P5" s="84"/>
+      <c r="Q5" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="60"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="64" t="s">
+      <c r="R5" s="81"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="43" t="s">
         <v>8</v>
       </c>
       <c r="U5" s="1"/>
@@ -2061,10 +2089,10 @@
     </row>
     <row r="6" spans="1:27" ht="29.25" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="57"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="51"/>
       <c r="F6" s="3" t="s">
         <v>9</v>
       </c>
@@ -2107,7 +2135,7 @@
       <c r="S6" s="27">
         <v>17</v>
       </c>
-      <c r="T6" s="52"/>
+      <c r="T6" s="44"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
@@ -2122,10 +2150,10 @@
     </row>
     <row r="7" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="58"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="79"/>
       <c r="F7" s="7" t="s">
         <v>12</v>
       </c>
@@ -2168,7 +2196,7 @@
       <c r="S7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="T7" s="52"/>
+      <c r="T7" s="44"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -2181,18 +2209,18 @@
     </row>
     <row r="8" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="68" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="44"/>
+      <c r="B8" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="49"/>
       <c r="D8" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="79"/>
-      <c r="G8" s="72"/>
+        <v>29</v>
+      </c>
+      <c r="F8" s="64"/>
+      <c r="G8" s="57"/>
       <c r="H8" s="36" t="s">
         <v>10</v>
       </c>
@@ -2201,15 +2229,13 @@
       <c r="K8" s="20"/>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
-      <c r="N8" s="81" t="s">
-        <v>27</v>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="21"/>
       <c r="P8" s="21"/>
       <c r="Q8" s="21"/>
       <c r="R8" s="21"/>
-      <c r="S8" s="65" t="s">
-        <v>28</v>
+      <c r="S8" s="45" t="s">
+        <v>27</v>
       </c>
       <c r="T8" s="11"/>
       <c r="U8" s="1"/>
@@ -2220,16 +2246,16 @@
     </row>
     <row r="9" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="52"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="44"/>
       <c r="D9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="76"/>
-      <c r="G9" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F9" s="61"/>
+      <c r="G9" s="58"/>
       <c r="H9" s="36" t="s">
         <v>10</v>
       </c>
@@ -2238,12 +2264,12 @@
       <c r="K9" s="20"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
-      <c r="N9" s="66"/>
+      <c r="N9" s="19"/>
       <c r="O9" s="19"/>
       <c r="P9" s="19"/>
       <c r="Q9" s="19"/>
       <c r="R9" s="19"/>
-      <c r="S9" s="66"/>
+      <c r="S9" s="46"/>
       <c r="T9" s="11"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -2253,16 +2279,16 @@
     </row>
     <row r="10" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="52"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="44"/>
       <c r="D10" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="76"/>
-      <c r="G10" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F10" s="61"/>
+      <c r="G10" s="58"/>
       <c r="H10" s="36" t="s">
         <v>10</v>
       </c>
@@ -2273,12 +2299,12 @@
       <c r="K10" s="20"/>
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
-      <c r="N10" s="66"/>
+      <c r="N10" s="19"/>
       <c r="O10" s="19"/>
       <c r="P10" s="19"/>
       <c r="Q10" s="19"/>
       <c r="R10" s="19"/>
-      <c r="S10" s="66"/>
+      <c r="S10" s="46"/>
       <c r="T10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
@@ -2287,16 +2313,16 @@
     </row>
     <row r="11" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="52"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="44"/>
       <c r="D11" s="12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="76"/>
-      <c r="G11" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F11" s="61"/>
+      <c r="G11" s="58"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
@@ -2305,14 +2331,14 @@
         <v>10</v>
       </c>
       <c r="M11" s="19"/>
-      <c r="N11" s="66"/>
+      <c r="N11" s="19"/>
       <c r="O11" s="19"/>
       <c r="P11" s="19"/>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
-      <c r="S11" s="66"/>
+      <c r="S11" s="46"/>
       <c r="T11" s="41" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
@@ -2322,16 +2348,16 @@
     </row>
     <row r="12" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="86" t="s">
-        <v>52</v>
+      <c r="B12" s="51"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="42" t="s">
+        <v>49</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="80"/>
-      <c r="G12" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F12" s="65"/>
+      <c r="G12" s="58"/>
       <c r="H12" s="19"/>
       <c r="I12" s="21"/>
       <c r="J12" s="21"/>
@@ -2340,14 +2366,14 @@
         <v>10</v>
       </c>
       <c r="M12" s="19"/>
-      <c r="N12" s="66"/>
+      <c r="N12" s="19"/>
       <c r="O12" s="19"/>
       <c r="P12" s="19"/>
       <c r="Q12" s="19"/>
       <c r="R12" s="19"/>
-      <c r="S12" s="66"/>
+      <c r="S12" s="46"/>
       <c r="T12" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
@@ -2357,16 +2383,16 @@
     </row>
     <row r="13" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="52"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="44"/>
       <c r="D13" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="80"/>
-      <c r="G13" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F13" s="65"/>
+      <c r="G13" s="58"/>
       <c r="H13" s="19"/>
       <c r="I13" s="36" t="s">
         <v>10</v>
@@ -2375,20 +2401,20 @@
         <v>10</v>
       </c>
       <c r="K13" s="36" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N13" s="66"/>
+      <c r="N13" s="19"/>
       <c r="O13" s="19"/>
       <c r="P13" s="19"/>
       <c r="Q13" s="19"/>
       <c r="R13" s="19"/>
-      <c r="S13" s="66"/>
+      <c r="S13" s="46"/>
       <c r="T13" s="11"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -2398,16 +2424,16 @@
     </row>
     <row r="14" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="52"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="44"/>
       <c r="D14" s="13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="80"/>
-      <c r="G14" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F14" s="65"/>
+      <c r="G14" s="58"/>
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
       <c r="J14" s="19"/>
@@ -2416,12 +2442,12 @@
         <v>10</v>
       </c>
       <c r="M14" s="19"/>
-      <c r="N14" s="66"/>
+      <c r="N14" s="19"/>
       <c r="O14" s="19"/>
       <c r="P14" s="19"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="19"/>
-      <c r="S14" s="66"/>
+      <c r="S14" s="46"/>
       <c r="T14" s="11"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
@@ -2431,16 +2457,16 @@
     </row>
     <row r="15" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="52"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="44"/>
       <c r="D15" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="80"/>
-      <c r="G15" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F15" s="65"/>
+      <c r="G15" s="58"/>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
       <c r="J15" s="19"/>
@@ -2451,12 +2477,12 @@
         <v>10</v>
       </c>
       <c r="M15" s="19"/>
-      <c r="N15" s="66"/>
+      <c r="N15" s="19"/>
       <c r="O15" s="19"/>
       <c r="P15" s="19"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
-      <c r="S15" s="66"/>
+      <c r="S15" s="46"/>
       <c r="T15" s="11"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
@@ -2466,29 +2492,33 @@
     </row>
     <row r="16" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="47"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="77"/>
-      <c r="G16" s="74"/>
+        <v>29</v>
+      </c>
+      <c r="F16" s="65"/>
+      <c r="G16" s="58"/>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="19"/>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
       <c r="M16" s="19"/>
-      <c r="N16" s="66"/>
+      <c r="N16" s="6" t="s">
+        <v>10</v>
+      </c>
       <c r="O16" s="19"/>
       <c r="P16" s="19"/>
       <c r="Q16" s="19"/>
       <c r="R16" s="19"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="11"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="86" t="s">
+        <v>64</v>
+      </c>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
@@ -2497,33 +2527,33 @@
     </row>
     <row r="17" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="9" t="s">
-        <v>42</v>
+      <c r="B17" s="52"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="79"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="62"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J17" s="21"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="66"/>
       <c r="O17" s="19"/>
       <c r="P17" s="19"/>
       <c r="Q17" s="19"/>
       <c r="R17" s="19"/>
-      <c r="S17" s="66"/>
-      <c r="T17" s="11"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="87" t="s">
+        <v>66</v>
+      </c>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
@@ -2532,30 +2562,32 @@
     </row>
     <row r="18" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
+      <c r="B18" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="49"/>
       <c r="D18" s="9" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="76"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="64"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="20"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="66"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="19"/>
       <c r="O18" s="19"/>
       <c r="P18" s="19"/>
       <c r="Q18" s="19"/>
       <c r="R18" s="19"/>
-      <c r="S18" s="66"/>
+      <c r="S18" s="46"/>
       <c r="T18" s="11"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
@@ -2565,30 +2597,30 @@
     </row>
     <row r="19" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="12" t="s">
-        <v>41</v>
+      <c r="B19" s="50"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="76"/>
-      <c r="G19" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F19" s="61"/>
+      <c r="G19" s="58"/>
       <c r="H19" s="19"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="6" t="s">
+      <c r="I19" s="40"/>
+      <c r="J19" s="36" t="s">
         <v>10</v>
       </c>
       <c r="K19" s="20"/>
       <c r="L19" s="19"/>
       <c r="M19" s="19"/>
-      <c r="N19" s="66"/>
+      <c r="N19" s="19"/>
       <c r="O19" s="19"/>
       <c r="P19" s="19"/>
       <c r="Q19" s="19"/>
       <c r="R19" s="19"/>
-      <c r="S19" s="66"/>
+      <c r="S19" s="46"/>
       <c r="T19" s="11"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
@@ -2598,30 +2630,30 @@
     </row>
     <row r="20" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="52"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="12" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="76"/>
-      <c r="G20" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F20" s="61"/>
+      <c r="G20" s="58"/>
       <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
+      <c r="I20" s="39"/>
       <c r="J20" s="6" t="s">
         <v>10</v>
       </c>
       <c r="K20" s="20"/>
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
-      <c r="N20" s="66"/>
+      <c r="N20" s="19"/>
       <c r="O20" s="19"/>
       <c r="P20" s="19"/>
       <c r="Q20" s="19"/>
       <c r="R20" s="19"/>
-      <c r="S20" s="66"/>
+      <c r="S20" s="46"/>
       <c r="T20" s="11"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -2631,30 +2663,30 @@
     </row>
     <row r="21" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="13" t="s">
-        <v>55</v>
+      <c r="B21" s="50"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="77"/>
-      <c r="G21" s="74"/>
+        <v>29</v>
+      </c>
+      <c r="F21" s="61"/>
+      <c r="G21" s="58"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
+      <c r="J21" s="6" t="s">
+        <v>10</v>
+      </c>
       <c r="K21" s="20"/>
       <c r="L21" s="19"/>
-      <c r="M21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="N21" s="66"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="19"/>
       <c r="P21" s="19"/>
       <c r="Q21" s="19"/>
       <c r="R21" s="19"/>
-      <c r="S21" s="66"/>
+      <c r="S21" s="46"/>
       <c r="T21" s="11"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -2664,35 +2696,31 @@
     </row>
     <row r="22" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="70" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="14" t="s">
-        <v>39</v>
+      <c r="B22" s="52"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="75"/>
-      <c r="G22" s="78"/>
+        <v>29</v>
+      </c>
+      <c r="F22" s="62"/>
+      <c r="G22" s="59"/>
       <c r="H22" s="19"/>
-      <c r="I22" s="36" t="s">
-        <v>10</v>
-      </c>
+      <c r="I22" s="19"/>
       <c r="J22" s="19"/>
       <c r="K22" s="20"/>
       <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="66"/>
+      <c r="M22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N22" s="19"/>
       <c r="O22" s="19"/>
       <c r="P22" s="19"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="19"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="41" t="s">
-        <v>47</v>
-      </c>
+      <c r="S22" s="46"/>
+      <c r="T22" s="11"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -2701,28 +2729,35 @@
     </row>
     <row r="23" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="51"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="12" t="s">
-        <v>40</v>
+      <c r="B23" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="49"/>
+      <c r="D23" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="76"/>
-      <c r="G23" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F23" s="60"/>
+      <c r="G23" s="63"/>
       <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
+      <c r="I23" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="19"/>
       <c r="K23" s="20"/>
       <c r="L23" s="19"/>
       <c r="M23" s="19"/>
-      <c r="N23" s="66"/>
+      <c r="N23" s="19"/>
       <c r="O23" s="19"/>
       <c r="P23" s="19"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="11"/>
+      <c r="S23" s="46"/>
+      <c r="T23" s="41" t="s">
+        <v>45</v>
+      </c>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -2731,24 +2766,27 @@
     </row>
     <row r="24" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="73"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="61"/>
+      <c r="G24" s="58"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
       <c r="K24" s="20"/>
       <c r="L24" s="19"/>
       <c r="M24" s="19"/>
-      <c r="N24" s="66"/>
+      <c r="N24" s="19"/>
       <c r="O24" s="19"/>
       <c r="P24" s="19"/>
       <c r="Q24" s="19"/>
       <c r="R24" s="19"/>
-      <c r="S24" s="66"/>
+      <c r="S24" s="46"/>
       <c r="T24" s="11"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
@@ -2758,28 +2796,28 @@
     </row>
     <row r="25" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="52"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="44"/>
       <c r="D25" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F25" s="76"/>
-      <c r="G25" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F25" s="61"/>
+      <c r="G25" s="58"/>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
       <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
+      <c r="K25" s="20"/>
       <c r="L25" s="39"/>
       <c r="M25" s="19"/>
-      <c r="N25" s="66"/>
+      <c r="N25" s="19"/>
       <c r="O25" s="19"/>
       <c r="P25" s="19"/>
       <c r="Q25" s="19"/>
       <c r="R25" s="19"/>
-      <c r="S25" s="66"/>
+      <c r="S25" s="46"/>
       <c r="T25" s="11"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
@@ -2789,24 +2827,30 @@
     </row>
     <row r="26" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="73"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="61"/>
+      <c r="G26" s="58"/>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="19"/>
-      <c r="K26" s="20"/>
+      <c r="K26" s="19"/>
       <c r="L26" s="19"/>
       <c r="M26" s="19"/>
-      <c r="N26" s="66"/>
+      <c r="N26" s="6" t="s">
+        <v>10</v>
+      </c>
       <c r="O26" s="19"/>
       <c r="P26" s="19"/>
       <c r="Q26" s="19"/>
       <c r="R26" s="19"/>
-      <c r="S26" s="66"/>
+      <c r="S26" s="46"/>
       <c r="T26" s="11"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
@@ -2816,23 +2860,24 @@
     </row>
     <row r="27" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="13"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="12"/>
       <c r="E27" s="10"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="74"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="58"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
       <c r="K27" s="20"/>
       <c r="L27" s="19"/>
       <c r="M27" s="19"/>
-      <c r="N27" s="66"/>
+      <c r="N27" s="19"/>
       <c r="O27" s="19"/>
       <c r="P27" s="19"/>
       <c r="Q27" s="19"/>
       <c r="R27" s="19"/>
-      <c r="S27" s="66"/>
+      <c r="S27" s="46"/>
       <c r="T27" s="11"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
@@ -2842,35 +2887,24 @@
     </row>
     <row r="28" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="71" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="44"/>
-      <c r="D28" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F28" s="75"/>
-      <c r="G28" s="78"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="59"/>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
       <c r="K28" s="20"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="N28" s="66"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
       <c r="O28" s="19"/>
       <c r="P28" s="19"/>
       <c r="Q28" s="19"/>
       <c r="R28" s="19"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="11" t="s">
-        <v>60</v>
-      </c>
+      <c r="S28" s="46"/>
+      <c r="T28" s="11"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
@@ -2879,30 +2913,35 @@
     </row>
     <row r="29" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="52"/>
+      <c r="B29" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="49"/>
       <c r="D29" s="14" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" s="76"/>
-      <c r="G29" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F29" s="60"/>
+      <c r="G29" s="63"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
-      <c r="J29" s="20"/>
+      <c r="J29" s="19"/>
       <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
+      <c r="L29" s="39"/>
       <c r="M29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N29" s="66"/>
+      <c r="N29" s="19"/>
       <c r="O29" s="19"/>
       <c r="P29" s="19"/>
       <c r="Q29" s="19"/>
       <c r="R29" s="19"/>
-      <c r="S29" s="66"/>
+      <c r="S29" s="46"/>
+      <c r="T29" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
@@ -2911,31 +2950,30 @@
     </row>
     <row r="30" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="12" t="s">
-        <v>37</v>
+      <c r="B30" s="50"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="76"/>
-      <c r="G30" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F30" s="61"/>
+      <c r="G30" s="58"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
+      <c r="J30" s="20"/>
       <c r="K30" s="20"/>
       <c r="L30" s="20"/>
       <c r="M30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N30" s="66"/>
+      <c r="N30" s="19"/>
       <c r="O30" s="19"/>
       <c r="P30" s="19"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="19"/>
-      <c r="S30" s="66"/>
-      <c r="T30" s="11"/>
+      <c r="S30" s="46"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
@@ -2944,28 +2982,30 @@
     </row>
     <row r="31" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="52"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="44"/>
       <c r="D31" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="76"/>
-      <c r="G31" s="73"/>
+        <v>29</v>
+      </c>
+      <c r="F31" s="61"/>
+      <c r="G31" s="58"/>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
       <c r="J31" s="19"/>
       <c r="K31" s="20"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="66"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N31" s="19"/>
       <c r="O31" s="19"/>
       <c r="P31" s="19"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
-      <c r="S31" s="66"/>
+      <c r="S31" s="46"/>
       <c r="T31" s="11"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
@@ -2975,24 +3015,30 @@
     </row>
     <row r="32" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="73"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" s="61"/>
+      <c r="G32" s="58"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
       <c r="K32" s="20"/>
       <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="66"/>
+      <c r="M32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" s="19"/>
       <c r="O32" s="19"/>
       <c r="P32" s="19"/>
       <c r="Q32" s="19"/>
       <c r="R32" s="19"/>
-      <c r="S32" s="66"/>
+      <c r="S32" s="46"/>
       <c r="T32" s="11"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
@@ -3002,98 +3048,114 @@
     </row>
     <row r="33" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="74"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="61"/>
+      <c r="G33" s="58"/>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
-      <c r="K33" s="37"/>
+      <c r="K33" s="20"/>
       <c r="L33" s="19"/>
       <c r="M33" s="19"/>
-      <c r="N33" s="82"/>
+      <c r="N33" s="6" t="s">
+        <v>10</v>
+      </c>
       <c r="O33" s="19"/>
       <c r="P33" s="19"/>
       <c r="Q33" s="19"/>
       <c r="R33" s="19"/>
-      <c r="S33" s="67"/>
-      <c r="T33" s="15"/>
+      <c r="S33" s="46"/>
+      <c r="T33" s="11"/>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="16.5" customHeight="1">
+    <row r="34" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="38"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="65"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="46"/>
+      <c r="T34" s="85"/>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
-    </row>
-    <row r="35" spans="1:26" ht="16.5" customHeight="1">
+    </row>
+    <row r="35" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="62"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="19"/>
+      <c r="S35" s="47"/>
+      <c r="T35" s="15"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
     </row>
     <row r="36" spans="1:26" ht="16.5" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="16"/>
+      <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
+      <c r="K36" s="38"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
@@ -3113,7 +3175,7 @@
     <row r="37" spans="1:26" ht="16.5" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="16"/>
+      <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -3225,7 +3287,7 @@
     <row r="41" spans="1:26" ht="16.5" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
+      <c r="C41" s="16"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -3253,7 +3315,7 @@
     <row r="42" spans="1:26" ht="16.5" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
+      <c r="C42" s="16"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -3282,8 +3344,8 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -3310,8 +3372,8 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -3450,8 +3512,8 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -3478,8 +3540,8 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -8626,8 +8688,62 @@
       <c r="Y233" s="1"/>
       <c r="Z233" s="1"/>
     </row>
-    <row r="234" spans="1:26" ht="15.75" customHeight="1"/>
-    <row r="235" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="234" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A234" s="1"/>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
+      <c r="E234" s="1"/>
+      <c r="F234" s="1"/>
+      <c r="G234" s="1"/>
+      <c r="H234" s="1"/>
+      <c r="I234" s="1"/>
+      <c r="J234" s="1"/>
+      <c r="K234" s="1"/>
+      <c r="L234" s="1"/>
+      <c r="M234" s="1"/>
+      <c r="N234" s="1"/>
+      <c r="O234" s="1"/>
+      <c r="P234" s="1"/>
+      <c r="Q234" s="1"/>
+      <c r="R234" s="1"/>
+      <c r="S234" s="1"/>
+      <c r="T234" s="1"/>
+      <c r="U234" s="1"/>
+      <c r="V234" s="1"/>
+      <c r="W234" s="1"/>
+      <c r="X234" s="1"/>
+      <c r="Y234" s="1"/>
+      <c r="Z234" s="1"/>
+    </row>
+    <row r="235" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A235" s="1"/>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
+      <c r="E235" s="1"/>
+      <c r="F235" s="1"/>
+      <c r="G235" s="1"/>
+      <c r="H235" s="1"/>
+      <c r="I235" s="1"/>
+      <c r="J235" s="1"/>
+      <c r="K235" s="1"/>
+      <c r="L235" s="1"/>
+      <c r="M235" s="1"/>
+      <c r="N235" s="1"/>
+      <c r="O235" s="1"/>
+      <c r="P235" s="1"/>
+      <c r="Q235" s="1"/>
+      <c r="R235" s="1"/>
+      <c r="S235" s="1"/>
+      <c r="T235" s="1"/>
+      <c r="U235" s="1"/>
+      <c r="V235" s="1"/>
+      <c r="W235" s="1"/>
+      <c r="X235" s="1"/>
+      <c r="Y235" s="1"/>
+      <c r="Z235" s="1"/>
+    </row>
     <row r="236" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="237" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="238" spans="1:26" ht="15.75" customHeight="1"/>
@@ -9392,24 +9508,10 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="T5:T7"/>
-    <mergeCell ref="S8:S33"/>
-    <mergeCell ref="B8:C16"/>
-    <mergeCell ref="B17:C21"/>
-    <mergeCell ref="B22:C27"/>
-    <mergeCell ref="B28:C33"/>
-    <mergeCell ref="G8:G16"/>
-    <mergeCell ref="F22:F27"/>
-    <mergeCell ref="G22:G27"/>
-    <mergeCell ref="F28:F33"/>
-    <mergeCell ref="G28:G33"/>
-    <mergeCell ref="F8:F16"/>
-    <mergeCell ref="N8:N33"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="G17:G21"/>
+  <mergeCells count="22">
     <mergeCell ref="B2:S3"/>
     <mergeCell ref="B4:S4"/>
     <mergeCell ref="B5:C7"/>
@@ -9417,6 +9519,21 @@
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="Q5:S5"/>
     <mergeCell ref="M5:P5"/>
+    <mergeCell ref="T5:T7"/>
+    <mergeCell ref="S8:S35"/>
+    <mergeCell ref="B8:C17"/>
+    <mergeCell ref="B18:C22"/>
+    <mergeCell ref="B23:C28"/>
+    <mergeCell ref="B29:C35"/>
+    <mergeCell ref="G8:G17"/>
+    <mergeCell ref="F23:F28"/>
+    <mergeCell ref="G23:G28"/>
+    <mergeCell ref="F29:F35"/>
+    <mergeCell ref="G29:G35"/>
+    <mergeCell ref="F8:F17"/>
+    <mergeCell ref="F18:F22"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="G18:G22"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/docs/상세개발계획서 AI담당.xlsx
+++ b/docs/상세개발계획서 AI담당.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sungjonghyun/3-1/산학프로젝트/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCC2A18-6FB9-E949-A222-9368238470C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6969B0C8-4881-DE48-807F-3DABE5676953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="70">
+  <si>
+    <t>3팀 [21의 4분의 3 조] 상세개발계획서</t>
+  </si>
   <si>
     <t>Task</t>
   </si>
@@ -103,181 +106,141 @@
     <t>미 진행</t>
   </si>
   <si>
+    <t>사진인식모델
+→ EfficientNet</t>
+  </si>
+  <si>
+    <t>2차 데이터셋 확보(32가지 식재료)</t>
+  </si>
+  <si>
+    <t>성종현</t>
+  </si>
+  <si>
     <t xml:space="preserve">최
 종
 발
 표
 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Efficientnet-E0 전이학습 train코드 생성</t>
+  </si>
+  <si>
+    <t>Efficientnet V2-m 으로 전이학습 모델 변경 및 정확도 확인</t>
+  </si>
+  <si>
+    <t>VLM 하이브리드 통합 모델</t>
+  </si>
+  <si>
+    <t>신뢰도 75%미만 시 VLM(Gemini) 추론 연동</t>
+  </si>
+  <si>
+    <t>자동라벨링(미인식 데이터 자동 라벨링 파이프라인 구축)</t>
+  </si>
+  <si>
+    <t>Self-improving 기반</t>
+  </si>
+  <si>
+    <t>클래스 증가를 위한 데이터셋 지속 확보</t>
+  </si>
+  <si>
+    <t>타 파트 연동 준비(백엔드 연동용 추론 결과 반환 규격)</t>
+  </si>
+  <si>
+    <t>AI 디렉터리 전면 개편 및 Git 연동 세팅</t>
+  </si>
+  <si>
+    <t>정확도에 대한 기준 데이터셋 정의 후 성능 테스트</t>
+  </si>
+  <si>
+    <t>한계점:학습/검증 데이터와 독립된 테스트셋 구축 어려움 존재, 추후 실환경 데이터 수집을 통한 별도 평가 예정</t>
+  </si>
+  <si>
+    <t>60개 클래스 학습 완료 모델(ver3)</t>
+  </si>
+  <si>
+    <t>최종 Val Acc: 94.73% (Epoch 17)</t>
+  </si>
+  <si>
+    <t>영수증인식모델
+→ 구글 document ai api</t>
+  </si>
+  <si>
+    <t>구글 Document AI API, gemini API 연동 진행</t>
+  </si>
+  <si>
+    <t>구글 Document AI API 테스트</t>
+  </si>
+  <si>
+    <t>영수증 사진 인식 후 추가학습 여부 판단</t>
+  </si>
+  <si>
+    <t>영수증 인식 텍스트 추출 정확도 확인</t>
+  </si>
+  <si>
+    <t>Git 연동 세팅</t>
+  </si>
+  <si>
+    <t>냉장고 전체인식
+→ Gemini Vision</t>
+  </si>
+  <si>
+    <t>기본 YOLO 성능 테스트</t>
+  </si>
+  <si>
+    <t>클래스 개수 부족</t>
+  </si>
+  <si>
+    <t>YOLO 개선모델 테스트 후 추가학습 여부 판단</t>
+  </si>
+  <si>
+    <t>vlm으로 냉장고 전체인식 비용 체크</t>
+  </si>
+  <si>
+    <t>냉장고 물체 감지 — Gemini Vision 구현</t>
+  </si>
+  <si>
+    <t>백앤드 연결            → FastAPI</t>
+  </si>
+  <si>
+    <t>FastAPI 서버 구축</t>
+  </si>
+  <si>
+    <t>ngrok 외부접속 , bearer 토큰 인증</t>
+  </si>
+  <si>
+    <t>사진인식모델 학습 완료 후 FastAPI 연동</t>
+  </si>
+  <si>
+    <t>영수증인식모델 완료 후 FastAPI 연동</t>
+  </si>
+  <si>
+    <t>냉장고 전체인식 모델 완료 후 연동</t>
+  </si>
+  <si>
+    <t>인프라 &lt;-&gt; AI 연동</t>
+  </si>
+  <si>
+    <t>Gemini API 타임아웃 설정</t>
+  </si>
+  <si>
+    <t>서버 사용자 로깅 추가</t>
+  </si>
+  <si>
+    <t>카테고리 공통 모듈 구축 (models/category.py)</t>
+  </si>
+  <si>
+    <t>클래스 60개 → 70개 확장 (신규 10개 클래스 추가)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Confidence Threshold 상향 조정 (75% → 80%) / 클래스 개수 증가에 따른 최적화</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
       <t>3</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="36"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>팀</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="36"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> [21</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="36"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="36"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="36"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>분의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="36"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="36"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>조</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="36"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="36"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상세개발계획서</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>성종현</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>사진인식모델
-→ EfficientNet</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>영수증인식모델
-→ 구글 document ai api</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Efficientnet-E0 전이학습 train코드 생성</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>클래스 증가를 위한 데이터셋 지속 확보</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>구글 Document AI API 테스트</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>백앤드 연결            → FastAPI</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>영수증인식모델 완료 후 FastAPI 연동</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 YOLO 성능 테스트</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>YOLO 개선모델 테스트 후 추가학습 여부 판단</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>영수증 사진 인식 후 추가학습 여부 판단</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>구글 Document AI API, gemini API 연동 진행</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 데이터셋 확보(32가지 식재료)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Efficientnet V2-m 으로 전이학습 모델 변경 및 정확도 확인</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>사진인식모델 학습 완료 후 FastAPI 연동</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>영수증 인식 텍스트 추출 정확도 확인</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -286,7 +249,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>클래스</t>
+      <t>개</t>
     </r>
     <r>
       <rPr>
@@ -305,7 +268,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>개수</t>
+      <t>방식</t>
     </r>
     <r>
       <rPr>
@@ -324,56 +287,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>부족</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>vlm으로 냉장고 전체인식 비용 체크</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>정확도에 대한 기준 데이터셋 정의 후 성능 테스트</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>VLM 하이브리드 통합 모델</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>자동라벨링(미인식 데이터 자동 라벨링 파이프라인 구축)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>타 파트 연동 준비(백엔드 연동용 추론 결과 반환 규격)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI 디렉터리 전면 개편 및 Git 연동 세팅</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Git 연동 세팅</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>√</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>FastAPI 서버 구축</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>신뢰도</t>
+      <t>파이프라인</t>
     </r>
     <r>
       <rPr>
@@ -382,7 +296,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 75%</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -392,13 +306,16 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>미만 시 VLM(Gemini) 추론 연동</t>
+      <t>중복</t>
     </r>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">Self-improving </t>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -408,13 +325,16 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>기반</t>
+      <t>코드</t>
     </r>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">ngrok </t>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -424,72 +344,16 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">외부접속 </t>
+      <t>제거</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, bearer </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>토큰 인증</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉장고 전체인식
-→ Gemini Vision</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉장고 물체 감지 — Gemini Vision 구현</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉장고 전체인식 모델 완료 후 연동</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>인프라 &lt;-&gt; AI 연동</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>서버 사용자 로깅 추가</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gemini API 타임아웃 설정</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>한계점:학습/검증 데이터와 독립된 테스트셋 구축 어려움 존재, 추후 실환경 데이터 수집을 통한 별도 평가 예정</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>60개 클래스 학습 완료 모델(ver3)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>최종 Val Acc: 94.73% (Epoch 17)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,11 +364,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -569,24 +428,8 @@
       <b/>
       <sz val="36"/>
       <color theme="1"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="36"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="36"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -617,7 +460,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -669,12 +512,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
         <bgColor rgb="FF2F5496"/>
       </patternFill>
     </fill>
@@ -685,22 +522,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="61">
+  <borders count="56">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -725,17 +551,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -753,39 +568,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -961,28 +743,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -1010,15 +770,6 @@
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1145,32 +896,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFFF0000"/>
       </left>
       <right style="thin">
@@ -1222,19 +947,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1387,15 +1099,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFFFFFFF"/>
       </left>
@@ -1421,286 +1124,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFFD965"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1910,21 +1640,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1001"/>
+  <dimension ref="A1:AA1003"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.1640625" customWidth="1"/>
-    <col min="2" max="2" width="8.5" customWidth="1"/>
-    <col min="3" max="3" width="6.5" customWidth="1"/>
-    <col min="4" max="4" width="49.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="19" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="77.33203125" customWidth="1"/>
-    <col min="21" max="22" width="5.1640625" customWidth="1"/>
-    <col min="23" max="23" width="9.33203125" customWidth="1"/>
-    <col min="24" max="26" width="5" customWidth="1"/>
+    <col min="1" max="1" width="5.1640625" style="45" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="45" customWidth="1"/>
+    <col min="3" max="3" width="6.5" style="45" customWidth="1"/>
+    <col min="4" max="4" width="49.1640625" style="45" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" style="45" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="45" bestFit="1" customWidth="1"/>
+    <col min="7" max="12" width="5.83203125" style="45" bestFit="1" customWidth="1"/>
+    <col min="13" max="19" width="6.83203125" style="45" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="77.33203125" style="45" customWidth="1"/>
+    <col min="21" max="22" width="5.1640625" style="45" customWidth="1"/>
+    <col min="23" max="23" width="9.33203125" style="45" customWidth="1"/>
+    <col min="24" max="26" width="5" style="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="16.5" customHeight="1">
@@ -1957,26 +1687,26 @@
     </row>
     <row r="2" spans="1:27" ht="42.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="49"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="61"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -1987,24 +1717,24 @@
     </row>
     <row r="3" spans="1:27" ht="42.75" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="53"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
+      <c r="M3" s="70"/>
+      <c r="N3" s="70"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="70"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="70"/>
+      <c r="S3" s="65"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -2015,24 +1745,24 @@
     </row>
     <row r="4" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -2043,42 +1773,42 @@
     </row>
     <row r="5" spans="1:27" ht="29.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="75" t="s">
+      <c r="B5" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="78" t="s">
+      <c r="C5" s="61"/>
+      <c r="D5" s="57" t="s">
         <v>2</v>
       </c>
+      <c r="E5" s="79" t="s">
+        <v>3</v>
+      </c>
       <c r="F5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="80" t="s">
+      <c r="H5" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="83"/>
-      <c r="O5" s="83"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="80" t="s">
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="81"/>
-      <c r="S5" s="82"/>
-      <c r="T5" s="43" t="s">
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="54" t="s">
         <v>8</v>
+      </c>
+      <c r="R5" s="55"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="72" t="s">
+        <v>9</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -2089,12 +1819,12 @@
     </row>
     <row r="6" spans="1:27" ht="29.25" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="51"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="62"/>
       <c r="F6" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="5">
         <v>28</v>
@@ -2135,68 +1865,68 @@
       <c r="S6" s="27">
         <v>17</v>
       </c>
-      <c r="T6" s="44"/>
+      <c r="T6" s="63"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="79"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="64"/>
       <c r="F7" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7" s="35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P7" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q7" s="28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R7" s="26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S7" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="T7" s="44"/>
+        <v>26</v>
+      </c>
+      <c r="T7" s="63"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -2204,25 +1934,25 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="6"/>
       <c r="AA7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="61"/>
+      <c r="D8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="64"/>
-      <c r="G8" s="57"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="51"/>
       <c r="H8" s="36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="20"/>
       <c r="J8" s="20"/>
@@ -2234,8 +1964,8 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="21"/>
       <c r="R8" s="21"/>
-      <c r="S8" s="45" t="s">
-        <v>27</v>
+      <c r="S8" s="68" t="s">
+        <v>31</v>
       </c>
       <c r="T8" s="11"/>
       <c r="U8" s="1"/>
@@ -2246,18 +1976,18 @@
     </row>
     <row r="9" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="44"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="63"/>
       <c r="D9" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="61"/>
-      <c r="G9" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F9" s="74"/>
+      <c r="G9" s="52"/>
       <c r="H9" s="36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="20"/>
       <c r="J9" s="20"/>
@@ -2269,7 +1999,7 @@
       <c r="P9" s="19"/>
       <c r="Q9" s="19"/>
       <c r="R9" s="19"/>
-      <c r="S9" s="46"/>
+      <c r="S9" s="69"/>
       <c r="T9" s="11"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -2279,21 +2009,21 @@
     </row>
     <row r="10" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="44"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="12" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="61"/>
-      <c r="G10" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F10" s="74"/>
+      <c r="G10" s="52"/>
       <c r="H10" s="36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="20"/>
@@ -2304,7 +2034,7 @@
       <c r="P10" s="19"/>
       <c r="Q10" s="19"/>
       <c r="R10" s="19"/>
-      <c r="S10" s="46"/>
+      <c r="S10" s="69"/>
       <c r="T10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
@@ -2313,22 +2043,22 @@
     </row>
     <row r="11" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="44"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="63"/>
       <c r="D11" s="12" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="61"/>
-      <c r="G11" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F11" s="74"/>
+      <c r="G11" s="52"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
-      <c r="K11" s="40"/>
+      <c r="K11" s="39"/>
       <c r="L11" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
@@ -2336,9 +2066,9 @@
       <c r="P11" s="19"/>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="41" t="s">
-        <v>55</v>
+      <c r="S11" s="69"/>
+      <c r="T11" s="40" t="s">
+        <v>35</v>
       </c>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
@@ -2348,22 +2078,22 @@
     </row>
     <row r="12" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="42" t="s">
-        <v>49</v>
+      <c r="B12" s="62"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="41" t="s">
+        <v>36</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="65"/>
-      <c r="G12" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F12" s="74"/>
+      <c r="G12" s="52"/>
       <c r="H12" s="19"/>
       <c r="I12" s="21"/>
       <c r="J12" s="21"/>
       <c r="K12" s="19"/>
       <c r="L12" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M12" s="19"/>
       <c r="N12" s="19"/>
@@ -2371,9 +2101,9 @@
       <c r="P12" s="19"/>
       <c r="Q12" s="19"/>
       <c r="R12" s="19"/>
-      <c r="S12" s="46"/>
+      <c r="S12" s="69"/>
       <c r="T12" s="11" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
@@ -2383,38 +2113,42 @@
     </row>
     <row r="13" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="44"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="63"/>
       <c r="D13" s="13" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="65"/>
-      <c r="G13" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F13" s="74"/>
+      <c r="G13" s="52"/>
       <c r="H13" s="19"/>
       <c r="I13" s="36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J13" s="36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
+        <v>11</v>
+      </c>
+      <c r="L13" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="M13" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="N13" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="O13" s="36" t="s">
+        <v>11</v>
+      </c>
       <c r="P13" s="19"/>
       <c r="Q13" s="19"/>
       <c r="R13" s="19"/>
-      <c r="S13" s="46"/>
+      <c r="S13" s="69"/>
       <c r="T13" s="11"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -2424,22 +2158,22 @@
     </row>
     <row r="14" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="44"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="63"/>
       <c r="D14" s="13" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="65"/>
-      <c r="G14" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F14" s="74"/>
+      <c r="G14" s="52"/>
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
       <c r="J14" s="19"/>
       <c r="K14" s="19"/>
       <c r="L14" s="36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M14" s="19"/>
       <c r="N14" s="19"/>
@@ -2447,7 +2181,7 @@
       <c r="P14" s="19"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="19"/>
-      <c r="S14" s="46"/>
+      <c r="S14" s="69"/>
       <c r="T14" s="11"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
@@ -2457,32 +2191,34 @@
     </row>
     <row r="15" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="44"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="63"/>
       <c r="D15" s="13" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F15" s="74"/>
+      <c r="G15" s="52"/>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
       <c r="J15" s="19"/>
       <c r="K15" s="36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M15" s="19"/>
       <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
+      <c r="O15" s="36" t="s">
+        <v>11</v>
+      </c>
       <c r="P15" s="19"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
-      <c r="S15" s="46"/>
+      <c r="S15" s="69"/>
       <c r="T15" s="11"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
@@ -2492,16 +2228,16 @@
     </row>
     <row r="16" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="44"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="63"/>
       <c r="D16" s="13" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F16" s="74"/>
+      <c r="G16" s="52"/>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="19"/>
@@ -2509,15 +2245,15 @@
       <c r="L16" s="19"/>
       <c r="M16" s="19"/>
       <c r="N16" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O16" s="19"/>
       <c r="P16" s="19"/>
       <c r="Q16" s="19"/>
       <c r="R16" s="19"/>
-      <c r="S16" s="46"/>
-      <c r="T16" s="86" t="s">
-        <v>64</v>
+      <c r="S16" s="69"/>
+      <c r="T16" s="43" t="s">
+        <v>42</v>
       </c>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
@@ -2527,16 +2263,16 @@
     </row>
     <row r="17" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="52"/>
-      <c r="C17" s="53"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="63"/>
       <c r="D17" s="13" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="62"/>
-      <c r="G17" s="59"/>
+        <v>30</v>
+      </c>
+      <c r="F17" s="74"/>
+      <c r="G17" s="52"/>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="19"/>
@@ -2544,15 +2280,15 @@
       <c r="L17" s="19"/>
       <c r="M17" s="19"/>
       <c r="N17" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O17" s="19"/>
       <c r="P17" s="19"/>
       <c r="Q17" s="19"/>
       <c r="R17" s="19"/>
-      <c r="S17" s="46"/>
-      <c r="T17" s="87" t="s">
-        <v>66</v>
+      <c r="S17" s="69"/>
+      <c r="T17" s="44" t="s">
+        <v>44</v>
       </c>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
@@ -2562,33 +2298,33 @@
     </row>
     <row r="18" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="9" t="s">
-        <v>40</v>
+      <c r="B18" s="64"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="64"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="J18" s="21"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
+        <v>30</v>
+      </c>
+      <c r="F18" s="75"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="P18" s="19"/>
       <c r="Q18" s="19"/>
       <c r="R18" s="19"/>
-      <c r="S18" s="46"/>
-      <c r="T18" s="11"/>
+      <c r="S18" s="69"/>
+      <c r="T18" s="12" t="s">
+        <v>68</v>
+      </c>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
@@ -2597,30 +2333,32 @@
     </row>
     <row r="19" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="44"/>
+      <c r="B19" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="61"/>
       <c r="D19" s="9" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="61"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="K19" s="20"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
+        <v>30</v>
+      </c>
+      <c r="F19" s="81"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="J19" s="21"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
       <c r="N19" s="19"/>
       <c r="O19" s="19"/>
       <c r="P19" s="19"/>
       <c r="Q19" s="19"/>
       <c r="R19" s="19"/>
-      <c r="S19" s="46"/>
+      <c r="S19" s="69"/>
       <c r="T19" s="11"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
@@ -2630,20 +2368,20 @@
     </row>
     <row r="20" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="12" t="s">
-        <v>39</v>
+      <c r="B20" s="62"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="61"/>
-      <c r="G20" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F20" s="74"/>
+      <c r="G20" s="52"/>
       <c r="H20" s="19"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="6" t="s">
-        <v>10</v>
+      <c r="J20" s="36" t="s">
+        <v>11</v>
       </c>
       <c r="K20" s="20"/>
       <c r="L20" s="19"/>
@@ -2653,7 +2391,7 @@
       <c r="P20" s="19"/>
       <c r="Q20" s="19"/>
       <c r="R20" s="19"/>
-      <c r="S20" s="46"/>
+      <c r="S20" s="69"/>
       <c r="T20" s="11"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -2663,20 +2401,20 @@
     </row>
     <row r="21" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="44"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="63"/>
       <c r="D21" s="12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="61"/>
-      <c r="G21" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F21" s="74"/>
+      <c r="G21" s="52"/>
       <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
+      <c r="I21" s="38"/>
       <c r="J21" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K21" s="20"/>
       <c r="L21" s="19"/>
@@ -2686,7 +2424,7 @@
       <c r="P21" s="19"/>
       <c r="Q21" s="19"/>
       <c r="R21" s="19"/>
-      <c r="S21" s="46"/>
+      <c r="S21" s="69"/>
       <c r="T21" s="11"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -2696,30 +2434,30 @@
     </row>
     <row r="22" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="52"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="13" t="s">
-        <v>52</v>
+      <c r="B22" s="62"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="62"/>
-      <c r="G22" s="59"/>
+        <v>30</v>
+      </c>
+      <c r="F22" s="74"/>
+      <c r="G22" s="52"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
+      <c r="J22" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="K22" s="20"/>
       <c r="L22" s="19"/>
-      <c r="M22" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="M22" s="19"/>
       <c r="N22" s="19"/>
       <c r="O22" s="19"/>
       <c r="P22" s="19"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="19"/>
-      <c r="S22" s="46"/>
+      <c r="S22" s="69"/>
       <c r="T22" s="11"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
@@ -2729,35 +2467,33 @@
     </row>
     <row r="23" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="14" t="s">
-        <v>37</v>
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="60"/>
-      <c r="G23" s="63"/>
+        <v>30</v>
+      </c>
+      <c r="F23" s="75"/>
+      <c r="G23" s="53"/>
       <c r="H23" s="19"/>
-      <c r="I23" s="36" t="s">
-        <v>10</v>
-      </c>
+      <c r="I23" s="19"/>
       <c r="J23" s="19"/>
       <c r="K23" s="20"/>
       <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
+      <c r="M23" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
+      <c r="O23" s="36" t="s">
+        <v>11</v>
+      </c>
       <c r="P23" s="19"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
-      <c r="S23" s="46"/>
-      <c r="T23" s="41" t="s">
-        <v>45</v>
-      </c>
+      <c r="S23" s="69"/>
+      <c r="T23" s="11"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -2766,18 +2502,23 @@
     </row>
     <row r="24" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="12" t="s">
-        <v>38</v>
+      <c r="B24" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="61"/>
+      <c r="D24" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="61"/>
-      <c r="G24" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F24" s="73"/>
+      <c r="G24" s="67"/>
       <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
+      <c r="I24" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="J24" s="19"/>
       <c r="K24" s="20"/>
       <c r="L24" s="19"/>
       <c r="M24" s="19"/>
@@ -2786,8 +2527,10 @@
       <c r="P24" s="19"/>
       <c r="Q24" s="19"/>
       <c r="R24" s="19"/>
-      <c r="S24" s="46"/>
-      <c r="T24" s="11"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="40" t="s">
+        <v>53</v>
+      </c>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
@@ -2796,28 +2539,29 @@
     </row>
     <row r="25" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="44"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="63"/>
       <c r="D25" s="12" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" s="61"/>
-      <c r="G25" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F25" s="74"/>
+      <c r="G25" s="52"/>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
       <c r="K25" s="20"/>
-      <c r="L25" s="39"/>
+      <c r="L25" s="19"/>
       <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
+      <c r="N25" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="O25" s="19"/>
       <c r="P25" s="19"/>
       <c r="Q25" s="19"/>
       <c r="R25" s="19"/>
-      <c r="S25" s="46"/>
+      <c r="S25" s="69"/>
       <c r="T25" s="11"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
@@ -2827,30 +2571,28 @@
     </row>
     <row r="26" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="44"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="63"/>
       <c r="D26" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F26" s="61"/>
-      <c r="G26" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F26" s="74"/>
+      <c r="G26" s="52"/>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="38"/>
       <c r="M26" s="19"/>
-      <c r="N26" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="N26" s="19"/>
       <c r="O26" s="19"/>
       <c r="P26" s="19"/>
       <c r="Q26" s="19"/>
       <c r="R26" s="19"/>
-      <c r="S26" s="46"/>
+      <c r="S26" s="69"/>
       <c r="T26" s="11"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
@@ -2860,24 +2602,30 @@
     </row>
     <row r="27" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="58"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="74"/>
+      <c r="G27" s="52"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
-      <c r="K27" s="20"/>
+      <c r="K27" s="19"/>
       <c r="L27" s="19"/>
       <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
+      <c r="N27" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="O27" s="19"/>
       <c r="P27" s="19"/>
       <c r="Q27" s="19"/>
       <c r="R27" s="19"/>
-      <c r="S27" s="46"/>
+      <c r="S27" s="69"/>
       <c r="T27" s="11"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
@@ -2887,23 +2635,30 @@
     </row>
     <row r="28" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="59"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="74"/>
+      <c r="G28" s="52"/>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
       <c r="K28" s="20"/>
       <c r="L28" s="19"/>
       <c r="M28" s="19"/>
       <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
+      <c r="O28" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="P28" s="19"/>
       <c r="Q28" s="19"/>
       <c r="R28" s="19"/>
-      <c r="S28" s="46"/>
+      <c r="S28" s="69"/>
       <c r="T28" s="11"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
@@ -2913,35 +2668,24 @@
     </row>
     <row r="29" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="49"/>
-      <c r="D29" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="60"/>
-      <c r="G29" s="63"/>
+      <c r="B29" s="64"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="53"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
       <c r="K29" s="20"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
       <c r="N29" s="19"/>
       <c r="O29" s="19"/>
       <c r="P29" s="19"/>
       <c r="Q29" s="19"/>
       <c r="R29" s="19"/>
-      <c r="S29" s="46"/>
-      <c r="T29" s="11" t="s">
-        <v>57</v>
-      </c>
+      <c r="S29" s="69"/>
+      <c r="T29" s="11"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
@@ -2950,30 +2694,35 @@
     </row>
     <row r="30" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="44"/>
+      <c r="B30" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="61"/>
       <c r="D30" s="14" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F30" s="61"/>
-      <c r="G30" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F30" s="73"/>
+      <c r="G30" s="67"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
-      <c r="J30" s="20"/>
+      <c r="J30" s="19"/>
       <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
+      <c r="L30" s="38"/>
       <c r="M30" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N30" s="19"/>
       <c r="O30" s="19"/>
       <c r="P30" s="19"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="19"/>
-      <c r="S30" s="46"/>
+      <c r="S30" s="69"/>
+      <c r="T30" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
@@ -2982,31 +2731,30 @@
     </row>
     <row r="31" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="12" t="s">
-        <v>36</v>
+      <c r="B31" s="62"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31" s="61"/>
-      <c r="G31" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F31" s="74"/>
+      <c r="G31" s="52"/>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
+      <c r="J31" s="20"/>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
       <c r="M31" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N31" s="19"/>
       <c r="O31" s="19"/>
       <c r="P31" s="19"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
-      <c r="S31" s="46"/>
-      <c r="T31" s="11"/>
+      <c r="S31" s="69"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
@@ -3015,30 +2763,30 @@
     </row>
     <row r="32" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="44"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="63"/>
       <c r="D32" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32" s="61"/>
-      <c r="G32" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F32" s="74"/>
+      <c r="G32" s="52"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
       <c r="K32" s="20"/>
-      <c r="L32" s="19"/>
+      <c r="L32" s="20"/>
       <c r="M32" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N32" s="19"/>
       <c r="O32" s="19"/>
       <c r="P32" s="19"/>
       <c r="Q32" s="19"/>
       <c r="R32" s="19"/>
-      <c r="S32" s="46"/>
+      <c r="S32" s="69"/>
       <c r="T32" s="11"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
@@ -3048,30 +2796,30 @@
     </row>
     <row r="33" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="44"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="63"/>
       <c r="D33" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" s="61"/>
-      <c r="G33" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F33" s="74"/>
+      <c r="G33" s="52"/>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="20"/>
       <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="M33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N33" s="19"/>
       <c r="O33" s="19"/>
       <c r="P33" s="19"/>
       <c r="Q33" s="19"/>
       <c r="R33" s="19"/>
-      <c r="S33" s="46"/>
+      <c r="S33" s="69"/>
       <c r="T33" s="11"/>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
@@ -3081,31 +2829,31 @@
     </row>
     <row r="34" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="44"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="63"/>
       <c r="D34" s="12" t="s">
         <v>63</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="65"/>
-      <c r="G34" s="58"/>
+        <v>30</v>
+      </c>
+      <c r="F34" s="74"/>
+      <c r="G34" s="52"/>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
-      <c r="K34" s="37"/>
+      <c r="K34" s="20"/>
       <c r="L34" s="19"/>
       <c r="M34" s="19"/>
       <c r="N34" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O34" s="19"/>
       <c r="P34" s="19"/>
       <c r="Q34" s="19"/>
       <c r="R34" s="19"/>
-      <c r="S34" s="46"/>
-      <c r="T34" s="85"/>
+      <c r="S34" s="69"/>
+      <c r="T34" s="11"/>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
@@ -3114,16 +2862,16 @@
     </row>
     <row r="35" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="53"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="63"/>
       <c r="D35" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F35" s="62"/>
-      <c r="G35" s="59"/>
+        <v>30</v>
+      </c>
+      <c r="F35" s="74"/>
+      <c r="G35" s="52"/>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
@@ -3131,96 +2879,109 @@
       <c r="L35" s="19"/>
       <c r="M35" s="19"/>
       <c r="N35" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O35" s="19"/>
       <c r="P35" s="19"/>
       <c r="Q35" s="19"/>
       <c r="R35" s="19"/>
-      <c r="S35" s="47"/>
-      <c r="T35" s="15"/>
+      <c r="S35" s="69"/>
+      <c r="T35" s="42"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="16.5" customHeight="1">
+    <row r="36" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
+      <c r="B36" s="62"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" s="74"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="19"/>
+      <c r="S36" s="69"/>
+      <c r="T36" s="42"/>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
-    </row>
-    <row r="37" spans="1:26" ht="16.5" customHeight="1">
+    </row>
+    <row r="37" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" s="75"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="19"/>
+      <c r="O37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="70"/>
+      <c r="T37" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-    </row>
-    <row r="38" spans="1:26" ht="16.5" customHeight="1">
+    </row>
+    <row r="38" spans="1:26" ht="35" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="47"/>
+      <c r="T38" s="15"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
@@ -3230,25 +2991,25 @@
     </row>
     <row r="39" spans="1:26" ht="16.5" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
+      <c r="B39" s="46"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="19"/>
+      <c r="S39" s="47"/>
+      <c r="T39" s="15"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
@@ -3258,25 +3019,25 @@
     </row>
     <row r="40" spans="1:26" ht="16.5" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="47"/>
+      <c r="T40" s="15"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
@@ -3286,25 +3047,25 @@
     </row>
     <row r="41" spans="1:26" ht="16.5" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
+      <c r="S41" s="47"/>
+      <c r="T41" s="15"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
@@ -3314,25 +3075,25 @@
     </row>
     <row r="42" spans="1:26" ht="16.5" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="19"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="19"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="19"/>
+      <c r="S42" s="47"/>
+      <c r="T42" s="15"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
@@ -3343,7 +3104,7 @@
     <row r="43" spans="1:26" ht="16.5" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
+      <c r="C43" s="16"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -3371,7 +3132,7 @@
     <row r="44" spans="1:26" ht="16.5" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
+      <c r="C44" s="16"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -3400,8 +3161,8 @@
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -3428,8 +3189,8 @@
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -3568,8 +3329,8 @@
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -3596,8 +3357,8 @@
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -8744,8 +8505,62 @@
       <c r="Y235" s="1"/>
       <c r="Z235" s="1"/>
     </row>
-    <row r="236" spans="1:26" ht="15.75" customHeight="1"/>
-    <row r="237" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="236" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A236" s="1"/>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
+      <c r="E236" s="1"/>
+      <c r="F236" s="1"/>
+      <c r="G236" s="1"/>
+      <c r="H236" s="1"/>
+      <c r="I236" s="1"/>
+      <c r="J236" s="1"/>
+      <c r="K236" s="1"/>
+      <c r="L236" s="1"/>
+      <c r="M236" s="1"/>
+      <c r="N236" s="1"/>
+      <c r="O236" s="1"/>
+      <c r="P236" s="1"/>
+      <c r="Q236" s="1"/>
+      <c r="R236" s="1"/>
+      <c r="S236" s="1"/>
+      <c r="T236" s="1"/>
+      <c r="U236" s="1"/>
+      <c r="V236" s="1"/>
+      <c r="W236" s="1"/>
+      <c r="X236" s="1"/>
+      <c r="Y236" s="1"/>
+      <c r="Z236" s="1"/>
+    </row>
+    <row r="237" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A237" s="1"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
+      <c r="E237" s="1"/>
+      <c r="F237" s="1"/>
+      <c r="G237" s="1"/>
+      <c r="H237" s="1"/>
+      <c r="I237" s="1"/>
+      <c r="J237" s="1"/>
+      <c r="K237" s="1"/>
+      <c r="L237" s="1"/>
+      <c r="M237" s="1"/>
+      <c r="N237" s="1"/>
+      <c r="O237" s="1"/>
+      <c r="P237" s="1"/>
+      <c r="Q237" s="1"/>
+      <c r="R237" s="1"/>
+      <c r="S237" s="1"/>
+      <c r="T237" s="1"/>
+      <c r="U237" s="1"/>
+      <c r="V237" s="1"/>
+      <c r="W237" s="1"/>
+      <c r="X237" s="1"/>
+      <c r="Y237" s="1"/>
+      <c r="Z237" s="1"/>
+    </row>
     <row r="238" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="239" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="240" spans="1:26" ht="15.75" customHeight="1"/>
@@ -9510,33 +9325,35 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="T5:T7"/>
+    <mergeCell ref="F30:F37"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="F24:F29"/>
     <mergeCell ref="B2:S3"/>
+    <mergeCell ref="B30:C37"/>
+    <mergeCell ref="E5:E7"/>
     <mergeCell ref="B4:S4"/>
+    <mergeCell ref="F8:F18"/>
     <mergeCell ref="B5:C7"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="F19:F23"/>
+    <mergeCell ref="G19:G23"/>
+    <mergeCell ref="Q5:S5"/>
     <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="T5:T7"/>
-    <mergeCell ref="S8:S35"/>
-    <mergeCell ref="B8:C17"/>
-    <mergeCell ref="B18:C22"/>
-    <mergeCell ref="B23:C28"/>
-    <mergeCell ref="B29:C35"/>
-    <mergeCell ref="G8:G17"/>
-    <mergeCell ref="F23:F28"/>
-    <mergeCell ref="G23:G28"/>
-    <mergeCell ref="F29:F35"/>
-    <mergeCell ref="G29:G35"/>
-    <mergeCell ref="F8:F17"/>
-    <mergeCell ref="F18:F22"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="G18:G22"/>
+    <mergeCell ref="B8:C18"/>
+    <mergeCell ref="B24:C29"/>
+    <mergeCell ref="G24:G29"/>
+    <mergeCell ref="S8:S37"/>
+    <mergeCell ref="G8:G18"/>
+    <mergeCell ref="G30:G37"/>
+    <mergeCell ref="B19:C23"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/docs/상세개발계획서 AI담당.xlsx
+++ b/docs/상세개발계획서 AI담당.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sungjonghyun/3-1/산학프로젝트/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6969B0C8-4881-DE48-807F-3DABE5676953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DC20A1-2457-3449-A7C2-4D62C45CB2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="76">
   <si>
     <t>3팀 [21의 4분의 3 조] 상세개발계획서</t>
   </si>
@@ -348,12 +348,140 @@
     </r>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
+  <si>
+    <t>70개 클래스 학습 진행(Ver4)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 batch 3~4초 소요 -&gt; 1에폭(796배치)에 약 40분 소요 -&gt; batch 증가 못함, num_workers 조정</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>API 응답 안정성과 결과 품질 향상</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>성종현</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>타임아웃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재시도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>카테고리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정규화 추가</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>클래스명 한글, 카테고리 영어 통일</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,6 +584,13 @@
       <sz val="11"/>
       <color rgb="FF0A0A0A"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -1217,7 +1352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1359,29 +1494,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1391,40 +1557,12 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1640,7 +1778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1003"/>
+  <dimension ref="A1:AA1005"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="45" customWidth="1"/>
@@ -1687,25 +1825,25 @@
     </row>
     <row r="2" spans="1:27" ht="42.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
       <c r="S2" s="61"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -1717,24 +1855,24 @@
     </row>
     <row r="3" spans="1:27" ht="42.75" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="70"/>
-      <c r="R3" s="70"/>
-      <c r="S3" s="65"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="64"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -1745,7 +1883,7 @@
     </row>
     <row r="4" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="80"/>
+      <c r="B4" s="68"/>
       <c r="C4" s="69"/>
       <c r="D4" s="69"/>
       <c r="E4" s="69"/>
@@ -1773,14 +1911,14 @@
     </row>
     <row r="5" spans="1:27" ht="29.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="71" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="61"/>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="67" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1789,25 +1927,25 @@
       <c r="G5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="82" t="s">
+      <c r="H5" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="54" t="s">
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="54" t="s">
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="55"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="72" t="s">
+      <c r="R5" s="57"/>
+      <c r="S5" s="58"/>
+      <c r="T5" s="51" t="s">
         <v>9</v>
       </c>
       <c r="U5" s="1"/>
@@ -1819,10 +1957,10 @@
     </row>
     <row r="6" spans="1:27" ht="29.25" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="62"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="62"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="66"/>
       <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
@@ -1865,7 +2003,7 @@
       <c r="S6" s="27">
         <v>17</v>
       </c>
-      <c r="T6" s="63"/>
+      <c r="T6" s="52"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
@@ -1880,10 +2018,10 @@
     </row>
     <row r="7" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="64"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="64"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="62"/>
       <c r="F7" s="7" t="s">
         <v>13</v>
       </c>
@@ -1926,7 +2064,7 @@
       <c r="S7" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="T7" s="63"/>
+      <c r="T7" s="52"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -1939,7 +2077,7 @@
     </row>
     <row r="8" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="80" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="61"/>
@@ -1949,8 +2087,8 @@
       <c r="E8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="81"/>
-      <c r="G8" s="51"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="75"/>
       <c r="H8" s="36" t="s">
         <v>11</v>
       </c>
@@ -1964,7 +2102,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="21"/>
       <c r="R8" s="21"/>
-      <c r="S8" s="68" t="s">
+      <c r="S8" s="83" t="s">
         <v>31</v>
       </c>
       <c r="T8" s="11"/>
@@ -1976,16 +2114,16 @@
     </row>
     <row r="9" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="63"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="74"/>
-      <c r="G9" s="52"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="76"/>
       <c r="H9" s="36" t="s">
         <v>11</v>
       </c>
@@ -2009,16 +2147,16 @@
     </row>
     <row r="10" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="62"/>
-      <c r="C10" s="63"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="52"/>
       <c r="D10" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="74"/>
-      <c r="G10" s="52"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="76"/>
       <c r="H10" s="36" t="s">
         <v>11</v>
       </c>
@@ -2043,16 +2181,16 @@
     </row>
     <row r="11" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="62"/>
-      <c r="C11" s="63"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="52"/>
       <c r="D11" s="12" t="s">
         <v>34</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="74"/>
-      <c r="G11" s="52"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="76"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
@@ -2078,16 +2216,16 @@
     </row>
     <row r="12" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="63"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="52"/>
       <c r="D12" s="41" t="s">
         <v>36</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="74"/>
-      <c r="G12" s="52"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="76"/>
       <c r="H12" s="19"/>
       <c r="I12" s="21"/>
       <c r="J12" s="21"/>
@@ -2113,16 +2251,16 @@
     </row>
     <row r="13" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="62"/>
-      <c r="C13" s="63"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="52"/>
       <c r="D13" s="13" t="s">
         <v>38</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="74"/>
-      <c r="G13" s="52"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="76"/>
       <c r="H13" s="19"/>
       <c r="I13" s="36" t="s">
         <v>11</v>
@@ -2158,16 +2296,16 @@
     </row>
     <row r="14" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="63"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="13" t="s">
         <v>39</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="74"/>
-      <c r="G14" s="52"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="76"/>
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
       <c r="J14" s="19"/>
@@ -2191,16 +2329,16 @@
     </row>
     <row r="15" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="63"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="52"/>
       <c r="D15" s="13" t="s">
         <v>40</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="74"/>
-      <c r="G15" s="52"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="76"/>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
       <c r="J15" s="19"/>
@@ -2228,16 +2366,16 @@
     </row>
     <row r="16" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="62"/>
-      <c r="C16" s="63"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="13" t="s">
         <v>41</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="74"/>
-      <c r="G16" s="52"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="76"/>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="19"/>
@@ -2263,16 +2401,16 @@
     </row>
     <row r="17" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="62"/>
-      <c r="C17" s="63"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="13" t="s">
         <v>43</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="74"/>
-      <c r="G17" s="52"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="76"/>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="19"/>
@@ -2298,16 +2436,16 @@
     </row>
     <row r="18" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="12" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="75"/>
-      <c r="G18" s="53"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="76"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
       <c r="J18" s="19"/>
@@ -2333,33 +2471,33 @@
     </row>
     <row r="19" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="71" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="61"/>
-      <c r="D19" s="9" t="s">
-        <v>46</v>
+      <c r="B19" s="62"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="81"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="J19" s="21"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
       <c r="N19" s="19"/>
       <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
+      <c r="P19" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="Q19" s="19"/>
       <c r="R19" s="19"/>
       <c r="S19" s="69"/>
-      <c r="T19" s="11"/>
+      <c r="T19" s="12" t="s">
+        <v>71</v>
+      </c>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
@@ -2368,24 +2506,26 @@
     </row>
     <row r="20" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="63"/>
+      <c r="B20" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="61"/>
       <c r="D20" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="74"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="36" t="s">
+      <c r="F20" s="70"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="K20" s="20"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
       <c r="N20" s="19"/>
       <c r="O20" s="19"/>
       <c r="P20" s="19"/>
@@ -2401,19 +2541,19 @@
     </row>
     <row r="21" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="63"/>
-      <c r="D21" s="12" t="s">
-        <v>48</v>
+      <c r="B21" s="66"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="74"/>
-      <c r="G21" s="52"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="76"/>
       <c r="H21" s="19"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="6" t="s">
+      <c r="I21" s="39"/>
+      <c r="J21" s="36" t="s">
         <v>11</v>
       </c>
       <c r="K21" s="20"/>
@@ -2434,18 +2574,18 @@
     </row>
     <row r="22" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="63"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="52"/>
       <c r="D22" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="74"/>
-      <c r="G22" s="52"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="76"/>
       <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
+      <c r="I22" s="38"/>
       <c r="J22" s="6" t="s">
         <v>11</v>
       </c>
@@ -2467,28 +2607,26 @@
     </row>
     <row r="23" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="13" t="s">
-        <v>50</v>
+      <c r="B23" s="66"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="75"/>
-      <c r="G23" s="53"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="76"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
+      <c r="J23" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="K23" s="20"/>
       <c r="L23" s="19"/>
-      <c r="M23" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="M23" s="19"/>
       <c r="N23" s="19"/>
-      <c r="O23" s="36" t="s">
-        <v>11</v>
-      </c>
+      <c r="O23" s="19"/>
       <c r="P23" s="19"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
@@ -2502,35 +2640,33 @@
     </row>
     <row r="24" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="66" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="61"/>
-      <c r="D24" s="14" t="s">
-        <v>52</v>
+      <c r="B24" s="62"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="73"/>
-      <c r="G24" s="67"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="77"/>
       <c r="H24" s="19"/>
-      <c r="I24" s="36" t="s">
-        <v>11</v>
-      </c>
+      <c r="I24" s="19"/>
       <c r="J24" s="19"/>
       <c r="K24" s="20"/>
       <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
+      <c r="M24" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
+      <c r="O24" s="36" t="s">
+        <v>11</v>
+      </c>
       <c r="P24" s="19"/>
       <c r="Q24" s="19"/>
       <c r="R24" s="19"/>
       <c r="S24" s="69"/>
-      <c r="T24" s="40" t="s">
-        <v>53</v>
-      </c>
+      <c r="T24" s="11"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
@@ -2539,30 +2675,35 @@
     </row>
     <row r="25" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="12" t="s">
-        <v>54</v>
+      <c r="B25" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="61"/>
+      <c r="D25" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="74"/>
-      <c r="G25" s="52"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="82"/>
       <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
+      <c r="I25" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="J25" s="19"/>
       <c r="K25" s="20"/>
       <c r="L25" s="19"/>
       <c r="M25" s="19"/>
-      <c r="N25" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="N25" s="19"/>
       <c r="O25" s="19"/>
       <c r="P25" s="19"/>
       <c r="Q25" s="19"/>
       <c r="R25" s="19"/>
       <c r="S25" s="69"/>
-      <c r="T25" s="11"/>
+      <c r="T25" s="40" t="s">
+        <v>53</v>
+      </c>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
@@ -2571,23 +2712,24 @@
     </row>
     <row r="26" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="63"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="74"/>
-      <c r="G26" s="52"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="76"/>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
       <c r="K26" s="20"/>
-      <c r="L26" s="38"/>
+      <c r="L26" s="19"/>
       <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
+      <c r="N26" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="O26" s="19"/>
       <c r="P26" s="19"/>
       <c r="Q26" s="19"/>
@@ -2602,25 +2744,23 @@
     </row>
     <row r="27" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="63"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="74"/>
-      <c r="G27" s="52"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="76"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="38"/>
       <c r="M27" s="19"/>
-      <c r="N27" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="N27" s="19"/>
       <c r="O27" s="19"/>
       <c r="P27" s="19"/>
       <c r="Q27" s="19"/>
@@ -2635,26 +2775,26 @@
     </row>
     <row r="28" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="13" t="s">
-        <v>50</v>
+      <c r="B28" s="66"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="74"/>
-      <c r="G28" s="52"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="76"/>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
-      <c r="K28" s="20"/>
+      <c r="K28" s="19"/>
       <c r="L28" s="19"/>
       <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="6" t="s">
+      <c r="N28" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="O28" s="19"/>
       <c r="P28" s="19"/>
       <c r="Q28" s="19"/>
       <c r="R28" s="19"/>
@@ -2668,19 +2808,26 @@
     </row>
     <row r="29" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="64"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="53"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="54"/>
+      <c r="G29" s="76"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
       <c r="K29" s="20"/>
       <c r="L29" s="19"/>
       <c r="M29" s="19"/>
       <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
+      <c r="O29" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="P29" s="19"/>
       <c r="Q29" s="19"/>
       <c r="R29" s="19"/>
@@ -2694,34 +2841,31 @@
     </row>
     <row r="30" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="78" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="14" t="s">
-        <v>58</v>
+      <c r="B30" s="62"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="73"/>
-      <c r="G30" s="67"/>
+        <v>73</v>
+      </c>
+      <c r="F30" s="55"/>
+      <c r="G30" s="77"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
       <c r="K30" s="20"/>
-      <c r="L30" s="38"/>
-      <c r="M30" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
       <c r="N30" s="19"/>
       <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
+      <c r="P30" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="Q30" s="19"/>
       <c r="R30" s="19"/>
       <c r="S30" s="69"/>
-      <c r="T30" s="11" t="s">
-        <v>59</v>
+      <c r="T30" s="40" t="s">
+        <v>74</v>
       </c>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
@@ -2731,21 +2875,23 @@
     </row>
     <row r="31" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="62"/>
-      <c r="C31" s="63"/>
+      <c r="B31" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="61"/>
       <c r="D31" s="14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F31" s="74"/>
-      <c r="G31" s="52"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="82"/>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
-      <c r="J31" s="20"/>
+      <c r="J31" s="19"/>
       <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
+      <c r="L31" s="38"/>
       <c r="M31" s="6" t="s">
         <v>11</v>
       </c>
@@ -2755,6 +2901,9 @@
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
       <c r="S31" s="69"/>
+      <c r="T31" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
@@ -2763,19 +2912,19 @@
     </row>
     <row r="32" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="62"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="12" t="s">
-        <v>61</v>
+      <c r="B32" s="66"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="74"/>
-      <c r="G32" s="52"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="76"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
+      <c r="J32" s="20"/>
       <c r="K32" s="20"/>
       <c r="L32" s="20"/>
       <c r="M32" s="6" t="s">
@@ -2787,7 +2936,6 @@
       <c r="Q32" s="19"/>
       <c r="R32" s="19"/>
       <c r="S32" s="69"/>
-      <c r="T32" s="11"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
@@ -2796,21 +2944,21 @@
     </row>
     <row r="33" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="62"/>
-      <c r="C33" s="63"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="52"/>
       <c r="D33" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F33" s="74"/>
-      <c r="G33" s="52"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="76"/>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="20"/>
-      <c r="L33" s="19"/>
+      <c r="L33" s="20"/>
       <c r="M33" s="6" t="s">
         <v>11</v>
       </c>
@@ -2829,25 +2977,25 @@
     </row>
     <row r="34" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="63"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="52"/>
       <c r="D34" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="74"/>
-      <c r="G34" s="52"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="76"/>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
       <c r="K34" s="20"/>
       <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="6" t="s">
+      <c r="M34" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="N34" s="19"/>
       <c r="O34" s="19"/>
       <c r="P34" s="19"/>
       <c r="Q34" s="19"/>
@@ -2862,20 +3010,20 @@
     </row>
     <row r="35" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="63"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="52"/>
       <c r="D35" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="74"/>
-      <c r="G35" s="52"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="76"/>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
-      <c r="K35" s="37"/>
+      <c r="K35" s="20"/>
       <c r="L35" s="19"/>
       <c r="M35" s="19"/>
       <c r="N35" s="6" t="s">
@@ -2886,7 +3034,7 @@
       <c r="Q35" s="19"/>
       <c r="R35" s="19"/>
       <c r="S35" s="69"/>
-      <c r="T35" s="42"/>
+      <c r="T35" s="11"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
@@ -2895,16 +3043,16 @@
     </row>
     <row r="36" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="62"/>
-      <c r="C36" s="63"/>
+      <c r="B36" s="66"/>
+      <c r="C36" s="52"/>
       <c r="D36" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="74"/>
-      <c r="G36" s="52"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="76"/>
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
@@ -2928,96 +3076,105 @@
     </row>
     <row r="37" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="64"/>
-      <c r="C37" s="65"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="52"/>
       <c r="D37" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F37" s="75"/>
-      <c r="G37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="76"/>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
       <c r="K37" s="37"/>
       <c r="L37" s="19"/>
       <c r="M37" s="19"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="6" t="s">
+      <c r="N37" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="O37" s="19"/>
       <c r="P37" s="19"/>
       <c r="Q37" s="19"/>
       <c r="R37" s="19"/>
-      <c r="S37" s="70"/>
-      <c r="T37" s="15" t="s">
-        <v>69</v>
-      </c>
+      <c r="S37" s="69"/>
+      <c r="T37" s="42"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="35" customHeight="1">
+    <row r="38" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="50"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" s="54"/>
+      <c r="G38" s="76"/>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
       <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
+      <c r="K38" s="37"/>
       <c r="L38" s="19"/>
       <c r="M38" s="19"/>
       <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
+      <c r="O38" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="P38" s="19"/>
       <c r="Q38" s="19"/>
       <c r="R38" s="19"/>
-      <c r="S38" s="47"/>
-      <c r="T38" s="15"/>
+      <c r="S38" s="69"/>
+      <c r="T38" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-    </row>
-    <row r="39" spans="1:26" ht="16.5" customHeight="1">
+    </row>
+    <row r="39" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="48"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="50"/>
+      <c r="B39" s="62"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="55"/>
+      <c r="G39" s="77"/>
       <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
       <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
+      <c r="K39" s="37"/>
       <c r="L39" s="19"/>
       <c r="M39" s="19"/>
       <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
+      <c r="O39" s="85"/>
+      <c r="P39" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="Q39" s="19"/>
       <c r="R39" s="19"/>
-      <c r="S39" s="47"/>
+      <c r="S39" s="63"/>
       <c r="T39" s="15"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
-    </row>
-    <row r="40" spans="1:26" ht="16.5" customHeight="1">
+    </row>
+    <row r="40" spans="1:26" ht="35" customHeight="1" thickBot="1">
       <c r="A40" s="1"/>
       <c r="B40" s="46"/>
       <c r="C40" s="48"/>
@@ -3045,7 +3202,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="16.5" customHeight="1">
+    <row r="41" spans="1:26" ht="16.5" customHeight="1" thickBot="1">
       <c r="A41" s="1"/>
       <c r="B41" s="46"/>
       <c r="C41" s="48"/>
@@ -3103,25 +3260,25 @@
     </row>
     <row r="43" spans="1:26" ht="16.5" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="19"/>
+      <c r="O43" s="19"/>
+      <c r="P43" s="19"/>
+      <c r="Q43" s="19"/>
+      <c r="R43" s="19"/>
+      <c r="S43" s="47"/>
+      <c r="T43" s="15"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
@@ -3131,25 +3288,25 @@
     </row>
     <row r="44" spans="1:26" ht="16.5" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="19"/>
+      <c r="P44" s="19"/>
+      <c r="Q44" s="19"/>
+      <c r="R44" s="19"/>
+      <c r="S44" s="47"/>
+      <c r="T44" s="15"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
@@ -3160,7 +3317,7 @@
     <row r="45" spans="1:26" ht="16.5" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
+      <c r="C45" s="16"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -3188,7 +3345,7 @@
     <row r="46" spans="1:26" ht="16.5" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
+      <c r="C46" s="16"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -3217,8 +3374,8 @@
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -3245,8 +3402,8 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -3385,8 +3542,8 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -3413,8 +3570,8 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -8561,8 +8718,62 @@
       <c r="Y237" s="1"/>
       <c r="Z237" s="1"/>
     </row>
-    <row r="238" spans="1:26" ht="15.75" customHeight="1"/>
-    <row r="239" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="238" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
+      <c r="E238" s="1"/>
+      <c r="F238" s="1"/>
+      <c r="G238" s="1"/>
+      <c r="H238" s="1"/>
+      <c r="I238" s="1"/>
+      <c r="J238" s="1"/>
+      <c r="K238" s="1"/>
+      <c r="L238" s="1"/>
+      <c r="M238" s="1"/>
+      <c r="N238" s="1"/>
+      <c r="O238" s="1"/>
+      <c r="P238" s="1"/>
+      <c r="Q238" s="1"/>
+      <c r="R238" s="1"/>
+      <c r="S238" s="1"/>
+      <c r="T238" s="1"/>
+      <c r="U238" s="1"/>
+      <c r="V238" s="1"/>
+      <c r="W238" s="1"/>
+      <c r="X238" s="1"/>
+      <c r="Y238" s="1"/>
+      <c r="Z238" s="1"/>
+    </row>
+    <row r="239" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A239" s="1"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
+      <c r="E239" s="1"/>
+      <c r="F239" s="1"/>
+      <c r="G239" s="1"/>
+      <c r="H239" s="1"/>
+      <c r="I239" s="1"/>
+      <c r="J239" s="1"/>
+      <c r="K239" s="1"/>
+      <c r="L239" s="1"/>
+      <c r="M239" s="1"/>
+      <c r="N239" s="1"/>
+      <c r="O239" s="1"/>
+      <c r="P239" s="1"/>
+      <c r="Q239" s="1"/>
+      <c r="R239" s="1"/>
+      <c r="S239" s="1"/>
+      <c r="T239" s="1"/>
+      <c r="U239" s="1"/>
+      <c r="V239" s="1"/>
+      <c r="W239" s="1"/>
+      <c r="X239" s="1"/>
+      <c r="Y239" s="1"/>
+      <c r="Z239" s="1"/>
+    </row>
     <row r="240" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="241" ht="15.75" customHeight="1"/>
     <row r="242" ht="15.75" customHeight="1"/>
@@ -9327,30 +9538,32 @@
     <row r="1001" ht="15.75" customHeight="1"/>
     <row r="1002" ht="15.75" customHeight="1"/>
     <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B25:C30"/>
+    <mergeCell ref="G25:G30"/>
+    <mergeCell ref="S8:S39"/>
+    <mergeCell ref="G8:G19"/>
+    <mergeCell ref="G31:G39"/>
+    <mergeCell ref="B20:C24"/>
     <mergeCell ref="T5:T7"/>
-    <mergeCell ref="F30:F37"/>
+    <mergeCell ref="F31:F39"/>
     <mergeCell ref="M5:P5"/>
-    <mergeCell ref="F24:F29"/>
+    <mergeCell ref="F25:F30"/>
     <mergeCell ref="B2:S3"/>
-    <mergeCell ref="B30:C37"/>
+    <mergeCell ref="B31:C39"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="B4:S4"/>
-    <mergeCell ref="F8:F18"/>
+    <mergeCell ref="F8:F19"/>
     <mergeCell ref="B5:C7"/>
     <mergeCell ref="H5:L5"/>
-    <mergeCell ref="F19:F23"/>
-    <mergeCell ref="G19:G23"/>
+    <mergeCell ref="F20:F24"/>
+    <mergeCell ref="G20:G24"/>
     <mergeCell ref="Q5:S5"/>
     <mergeCell ref="D5:D7"/>
-    <mergeCell ref="B8:C18"/>
-    <mergeCell ref="B24:C29"/>
-    <mergeCell ref="G24:G29"/>
-    <mergeCell ref="S8:S37"/>
-    <mergeCell ref="G8:G18"/>
-    <mergeCell ref="G30:G37"/>
-    <mergeCell ref="B19:C23"/>
+    <mergeCell ref="B8:C19"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/docs/상세개발계획서 AI담당.xlsx
+++ b/docs/상세개발계획서 AI담당.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sungjonghyun/3-1/산학프로젝트/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DC20A1-2457-3449-A7C2-4D62C45CB2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46DE004-57B2-0340-B1B2-12486BC355BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="77">
   <si>
     <t>3팀 [21의 4분의 3 조] 상세개발계획서</t>
   </si>
@@ -353,10 +353,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>1 batch 3~4초 소요 -&gt; 1에폭(796배치)에 약 40분 소요 -&gt; batch 증가 못함, num_workers 조정</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>API 응답 안정성과 결과 품질 향상</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -474,6 +470,61 @@
   </si>
   <si>
     <t>클래스명 한글, 카테고리 영어 통일</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백엔드에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한글로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전송</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 batch 3~4초 소요 -&gt; 1에폭(796배치)에 40분 이상 소요 -&gt; batch 증가 못함, num_workers 조정</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1352,7 +1403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1494,10 +1545,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1512,21 +1589,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1538,29 +1609,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1789,7 +1843,7 @@
     <col min="6" max="6" width="6.6640625" style="45" bestFit="1" customWidth="1"/>
     <col min="7" max="12" width="5.83203125" style="45" bestFit="1" customWidth="1"/>
     <col min="13" max="19" width="6.83203125" style="45" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="77.33203125" style="45" customWidth="1"/>
+    <col min="20" max="20" width="78.1640625" style="45" customWidth="1"/>
     <col min="21" max="22" width="5.1640625" style="45" customWidth="1"/>
     <col min="23" max="23" width="9.33203125" style="45" customWidth="1"/>
     <col min="24" max="26" width="5" style="45" customWidth="1"/>
@@ -1825,26 +1879,26 @@
     </row>
     <row r="2" spans="1:27" ht="42.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="61"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="53"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -1855,7 +1909,7 @@
     </row>
     <row r="3" spans="1:27" ht="42.75" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
+      <c r="B3" s="56"/>
       <c r="C3" s="63"/>
       <c r="D3" s="63"/>
       <c r="E3" s="63"/>
@@ -1872,7 +1926,7 @@
       <c r="P3" s="63"/>
       <c r="Q3" s="63"/>
       <c r="R3" s="63"/>
-      <c r="S3" s="64"/>
+      <c r="S3" s="57"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -1883,24 +1937,24 @@
     </row>
     <row r="4" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1911,14 +1965,14 @@
     </row>
     <row r="5" spans="1:27" ht="29.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="71" t="s">
+      <c r="C5" s="53"/>
+      <c r="D5" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="76" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1927,25 +1981,25 @@
       <c r="G5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="72" t="s">
+      <c r="H5" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="56" t="s">
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="56" t="s">
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="57"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="51" t="s">
+      <c r="R5" s="71"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="66" t="s">
         <v>9</v>
       </c>
       <c r="U5" s="1"/>
@@ -1957,10 +2011,10 @@
     </row>
     <row r="6" spans="1:27" ht="29.25" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="66"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="54"/>
       <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
@@ -2003,7 +2057,7 @@
       <c r="S6" s="27">
         <v>17</v>
       </c>
-      <c r="T6" s="52"/>
+      <c r="T6" s="55"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
@@ -2018,10 +2072,10 @@
     </row>
     <row r="7" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="62"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="62"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="56"/>
       <c r="F7" s="7" t="s">
         <v>13</v>
       </c>
@@ -2064,7 +2118,7 @@
       <c r="S7" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="T7" s="52"/>
+      <c r="T7" s="55"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -2077,18 +2131,18 @@
     </row>
     <row r="8" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="61"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="9" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="70"/>
-      <c r="G8" s="75"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="64"/>
       <c r="H8" s="36" t="s">
         <v>11</v>
       </c>
@@ -2102,7 +2156,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="21"/>
       <c r="R8" s="21"/>
-      <c r="S8" s="83" t="s">
+      <c r="S8" s="61" t="s">
         <v>31</v>
       </c>
       <c r="T8" s="11"/>
@@ -2114,16 +2168,16 @@
     </row>
     <row r="9" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="66"/>
-      <c r="C9" s="52"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="55"/>
       <c r="D9" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="76"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="59"/>
       <c r="H9" s="36" t="s">
         <v>11</v>
       </c>
@@ -2137,7 +2191,7 @@
       <c r="P9" s="19"/>
       <c r="Q9" s="19"/>
       <c r="R9" s="19"/>
-      <c r="S9" s="69"/>
+      <c r="S9" s="62"/>
       <c r="T9" s="11"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -2147,16 +2201,16 @@
     </row>
     <row r="10" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="52"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="55"/>
       <c r="D10" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="54"/>
-      <c r="G10" s="76"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="59"/>
       <c r="H10" s="36" t="s">
         <v>11</v>
       </c>
@@ -2172,7 +2226,7 @@
       <c r="P10" s="19"/>
       <c r="Q10" s="19"/>
       <c r="R10" s="19"/>
-      <c r="S10" s="69"/>
+      <c r="S10" s="62"/>
       <c r="T10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
@@ -2181,16 +2235,16 @@
     </row>
     <row r="11" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="52"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="55"/>
       <c r="D11" s="12" t="s">
         <v>34</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="54"/>
-      <c r="G11" s="76"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="59"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
@@ -2204,7 +2258,7 @@
       <c r="P11" s="19"/>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
-      <c r="S11" s="69"/>
+      <c r="S11" s="62"/>
       <c r="T11" s="40" t="s">
         <v>35</v>
       </c>
@@ -2216,16 +2270,16 @@
     </row>
     <row r="12" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="52"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="55"/>
       <c r="D12" s="41" t="s">
         <v>36</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="54"/>
-      <c r="G12" s="76"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="59"/>
       <c r="H12" s="19"/>
       <c r="I12" s="21"/>
       <c r="J12" s="21"/>
@@ -2239,7 +2293,7 @@
       <c r="P12" s="19"/>
       <c r="Q12" s="19"/>
       <c r="R12" s="19"/>
-      <c r="S12" s="69"/>
+      <c r="S12" s="62"/>
       <c r="T12" s="11" t="s">
         <v>37</v>
       </c>
@@ -2251,16 +2305,16 @@
     </row>
     <row r="13" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="52"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="55"/>
       <c r="D13" s="13" t="s">
         <v>38</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="54"/>
-      <c r="G13" s="76"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="59"/>
       <c r="H13" s="19"/>
       <c r="I13" s="36" t="s">
         <v>11</v>
@@ -2286,7 +2340,7 @@
       <c r="P13" s="19"/>
       <c r="Q13" s="19"/>
       <c r="R13" s="19"/>
-      <c r="S13" s="69"/>
+      <c r="S13" s="62"/>
       <c r="T13" s="11"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -2296,16 +2350,16 @@
     </row>
     <row r="14" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="52"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="55"/>
       <c r="D14" s="13" t="s">
         <v>39</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="54"/>
-      <c r="G14" s="76"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="59"/>
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
       <c r="J14" s="19"/>
@@ -2319,7 +2373,7 @@
       <c r="P14" s="19"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="19"/>
-      <c r="S14" s="69"/>
+      <c r="S14" s="62"/>
       <c r="T14" s="11"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
@@ -2329,16 +2383,16 @@
     </row>
     <row r="15" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="52"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="55"/>
       <c r="D15" s="13" t="s">
         <v>40</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="54"/>
-      <c r="G15" s="76"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="59"/>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
       <c r="J15" s="19"/>
@@ -2356,7 +2410,7 @@
       <c r="P15" s="19"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
-      <c r="S15" s="69"/>
+      <c r="S15" s="62"/>
       <c r="T15" s="11"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
@@ -2366,16 +2420,16 @@
     </row>
     <row r="16" spans="1:27" ht="29.25" customHeight="1" thickBot="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="52"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="55"/>
       <c r="D16" s="13" t="s">
         <v>41</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="54"/>
-      <c r="G16" s="76"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="59"/>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="19"/>
@@ -2389,7 +2443,7 @@
       <c r="P16" s="19"/>
       <c r="Q16" s="19"/>
       <c r="R16" s="19"/>
-      <c r="S16" s="69"/>
+      <c r="S16" s="62"/>
       <c r="T16" s="43" t="s">
         <v>42</v>
       </c>
@@ -2401,16 +2455,16 @@
     </row>
     <row r="17" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="52"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="55"/>
       <c r="D17" s="13" t="s">
         <v>43</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="54"/>
-      <c r="G17" s="76"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="59"/>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="19"/>
@@ -2424,7 +2478,7 @@
       <c r="P17" s="19"/>
       <c r="Q17" s="19"/>
       <c r="R17" s="19"/>
-      <c r="S17" s="69"/>
+      <c r="S17" s="62"/>
       <c r="T17" s="44" t="s">
         <v>44</v>
       </c>
@@ -2436,16 +2490,16 @@
     </row>
     <row r="18" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="52"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="55"/>
       <c r="D18" s="12" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="54"/>
-      <c r="G18" s="76"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="59"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
       <c r="J18" s="19"/>
@@ -2459,7 +2513,7 @@
       <c r="P18" s="19"/>
       <c r="Q18" s="19"/>
       <c r="R18" s="19"/>
-      <c r="S18" s="69"/>
+      <c r="S18" s="62"/>
       <c r="T18" s="12" t="s">
         <v>68</v>
       </c>
@@ -2471,16 +2525,16 @@
     </row>
     <row r="19" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="64"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="57"/>
       <c r="D19" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="55"/>
-      <c r="G19" s="77"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="60"/>
       <c r="H19" s="19"/>
       <c r="I19" s="19"/>
       <c r="J19" s="19"/>
@@ -2494,9 +2548,9 @@
       </c>
       <c r="Q19" s="19"/>
       <c r="R19" s="19"/>
-      <c r="S19" s="69"/>
+      <c r="S19" s="62"/>
       <c r="T19" s="12" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
@@ -2506,18 +2560,18 @@
     </row>
     <row r="20" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="61"/>
+      <c r="C20" s="53"/>
       <c r="D20" s="9" t="s">
         <v>46</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="70"/>
-      <c r="G20" s="75"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="64"/>
       <c r="H20" s="20"/>
       <c r="I20" s="36" t="s">
         <v>11</v>
@@ -2531,7 +2585,7 @@
       <c r="P20" s="19"/>
       <c r="Q20" s="19"/>
       <c r="R20" s="19"/>
-      <c r="S20" s="69"/>
+      <c r="S20" s="62"/>
       <c r="T20" s="11"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -2541,16 +2595,16 @@
     </row>
     <row r="21" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="52"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="55"/>
       <c r="D21" s="9" t="s">
         <v>47</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="54"/>
-      <c r="G21" s="76"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="59"/>
       <c r="H21" s="19"/>
       <c r="I21" s="39"/>
       <c r="J21" s="36" t="s">
@@ -2564,7 +2618,7 @@
       <c r="P21" s="19"/>
       <c r="Q21" s="19"/>
       <c r="R21" s="19"/>
-      <c r="S21" s="69"/>
+      <c r="S21" s="62"/>
       <c r="T21" s="11"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -2574,16 +2628,16 @@
     </row>
     <row r="22" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="52"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="55"/>
       <c r="D22" s="12" t="s">
         <v>48</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="54"/>
-      <c r="G22" s="76"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="59"/>
       <c r="H22" s="19"/>
       <c r="I22" s="38"/>
       <c r="J22" s="6" t="s">
@@ -2597,7 +2651,7 @@
       <c r="P22" s="19"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="19"/>
-      <c r="S22" s="69"/>
+      <c r="S22" s="62"/>
       <c r="T22" s="11"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
@@ -2607,16 +2661,16 @@
     </row>
     <row r="23" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="52"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="55"/>
       <c r="D23" s="12" t="s">
         <v>49</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="54"/>
-      <c r="G23" s="76"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="59"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
       <c r="J23" s="6" t="s">
@@ -2630,7 +2684,7 @@
       <c r="P23" s="19"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
-      <c r="S23" s="69"/>
+      <c r="S23" s="62"/>
       <c r="T23" s="11"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
@@ -2640,16 +2694,16 @@
     </row>
     <row r="24" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="64"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="57"/>
       <c r="D24" s="13" t="s">
         <v>50</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="55"/>
-      <c r="G24" s="77"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="60"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
       <c r="J24" s="19"/>
@@ -2665,7 +2719,7 @@
       <c r="P24" s="19"/>
       <c r="Q24" s="19"/>
       <c r="R24" s="19"/>
-      <c r="S24" s="69"/>
+      <c r="S24" s="62"/>
       <c r="T24" s="11"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
@@ -2675,18 +2729,18 @@
     </row>
     <row r="25" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="61"/>
+      <c r="C25" s="53"/>
       <c r="D25" s="14" t="s">
         <v>52</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="53"/>
-      <c r="G25" s="82"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="58"/>
       <c r="H25" s="19"/>
       <c r="I25" s="36" t="s">
         <v>11</v>
@@ -2700,7 +2754,7 @@
       <c r="P25" s="19"/>
       <c r="Q25" s="19"/>
       <c r="R25" s="19"/>
-      <c r="S25" s="69"/>
+      <c r="S25" s="62"/>
       <c r="T25" s="40" t="s">
         <v>53</v>
       </c>
@@ -2712,16 +2766,16 @@
     </row>
     <row r="26" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="66"/>
-      <c r="C26" s="52"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="55"/>
       <c r="D26" s="12" t="s">
         <v>54</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="54"/>
-      <c r="G26" s="76"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="59"/>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="K26" s="20"/>
@@ -2734,7 +2788,7 @@
       <c r="P26" s="19"/>
       <c r="Q26" s="19"/>
       <c r="R26" s="19"/>
-      <c r="S26" s="69"/>
+      <c r="S26" s="62"/>
       <c r="T26" s="11"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
@@ -2744,16 +2798,16 @@
     </row>
     <row r="27" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="66"/>
-      <c r="C27" s="52"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="55"/>
       <c r="D27" s="12" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="54"/>
-      <c r="G27" s="76"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="59"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
@@ -2765,7 +2819,7 @@
       <c r="P27" s="19"/>
       <c r="Q27" s="19"/>
       <c r="R27" s="19"/>
-      <c r="S27" s="69"/>
+      <c r="S27" s="62"/>
       <c r="T27" s="11"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
@@ -2775,16 +2829,16 @@
     </row>
     <row r="28" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="66"/>
-      <c r="C28" s="52"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
       <c r="D28" s="12" t="s">
         <v>56</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="54"/>
-      <c r="G28" s="76"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="59"/>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
@@ -2798,7 +2852,7 @@
       <c r="P28" s="19"/>
       <c r="Q28" s="19"/>
       <c r="R28" s="19"/>
-      <c r="S28" s="69"/>
+      <c r="S28" s="62"/>
       <c r="T28" s="11"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
@@ -2808,16 +2862,16 @@
     </row>
     <row r="29" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="66"/>
-      <c r="C29" s="52"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="55"/>
       <c r="D29" s="13" t="s">
         <v>50</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F29" s="54"/>
-      <c r="G29" s="76"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="59"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
@@ -2831,7 +2885,7 @@
       <c r="P29" s="19"/>
       <c r="Q29" s="19"/>
       <c r="R29" s="19"/>
-      <c r="S29" s="69"/>
+      <c r="S29" s="62"/>
       <c r="T29" s="11"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
@@ -2841,16 +2895,16 @@
     </row>
     <row r="30" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="64"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="57"/>
       <c r="D30" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="55"/>
-      <c r="G30" s="77"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="60"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
       <c r="K30" s="20"/>
@@ -2863,9 +2917,9 @@
       </c>
       <c r="Q30" s="19"/>
       <c r="R30" s="19"/>
-      <c r="S30" s="69"/>
+      <c r="S30" s="62"/>
       <c r="T30" s="40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
@@ -2875,18 +2929,18 @@
     </row>
     <row r="31" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="65" t="s">
+      <c r="B31" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="61"/>
+      <c r="C31" s="53"/>
       <c r="D31" s="14" t="s">
         <v>58</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F31" s="53"/>
-      <c r="G31" s="82"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="58"/>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
       <c r="J31" s="19"/>
@@ -2900,7 +2954,7 @@
       <c r="P31" s="19"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
-      <c r="S31" s="69"/>
+      <c r="S31" s="62"/>
       <c r="T31" s="11" t="s">
         <v>59</v>
       </c>
@@ -2912,16 +2966,16 @@
     </row>
     <row r="32" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="66"/>
-      <c r="C32" s="52"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="55"/>
       <c r="D32" s="14" t="s">
         <v>60</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="54"/>
-      <c r="G32" s="76"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="59"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
@@ -2935,7 +2989,7 @@
       <c r="P32" s="19"/>
       <c r="Q32" s="19"/>
       <c r="R32" s="19"/>
-      <c r="S32" s="69"/>
+      <c r="S32" s="62"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
@@ -2944,16 +2998,16 @@
     </row>
     <row r="33" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="66"/>
-      <c r="C33" s="52"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="55"/>
       <c r="D33" s="12" t="s">
         <v>61</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F33" s="54"/>
-      <c r="G33" s="76"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="59"/>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
@@ -2967,7 +3021,7 @@
       <c r="P33" s="19"/>
       <c r="Q33" s="19"/>
       <c r="R33" s="19"/>
-      <c r="S33" s="69"/>
+      <c r="S33" s="62"/>
       <c r="T33" s="11"/>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
@@ -2977,16 +3031,16 @@
     </row>
     <row r="34" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="66"/>
-      <c r="C34" s="52"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="55"/>
       <c r="D34" s="12" t="s">
         <v>62</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="54"/>
-      <c r="G34" s="76"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="59"/>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
@@ -3000,7 +3054,7 @@
       <c r="P34" s="19"/>
       <c r="Q34" s="19"/>
       <c r="R34" s="19"/>
-      <c r="S34" s="69"/>
+      <c r="S34" s="62"/>
       <c r="T34" s="11"/>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
@@ -3010,16 +3064,16 @@
     </row>
     <row r="35" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="66"/>
-      <c r="C35" s="52"/>
+      <c r="B35" s="54"/>
+      <c r="C35" s="55"/>
       <c r="D35" s="12" t="s">
         <v>63</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="54"/>
-      <c r="G35" s="76"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="59"/>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
@@ -3033,7 +3087,7 @@
       <c r="P35" s="19"/>
       <c r="Q35" s="19"/>
       <c r="R35" s="19"/>
-      <c r="S35" s="69"/>
+      <c r="S35" s="62"/>
       <c r="T35" s="11"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
@@ -3043,16 +3097,16 @@
     </row>
     <row r="36" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="66"/>
-      <c r="C36" s="52"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="55"/>
       <c r="D36" s="12" t="s">
         <v>64</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="54"/>
-      <c r="G36" s="76"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="59"/>
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
@@ -3066,7 +3120,7 @@
       <c r="P36" s="19"/>
       <c r="Q36" s="19"/>
       <c r="R36" s="19"/>
-      <c r="S36" s="69"/>
+      <c r="S36" s="62"/>
       <c r="T36" s="42"/>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
@@ -3076,16 +3130,16 @@
     </row>
     <row r="37" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="66"/>
-      <c r="C37" s="52"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="55"/>
       <c r="D37" s="12" t="s">
         <v>65</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F37" s="54"/>
-      <c r="G37" s="76"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="59"/>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
@@ -3099,7 +3153,7 @@
       <c r="P37" s="19"/>
       <c r="Q37" s="19"/>
       <c r="R37" s="19"/>
-      <c r="S37" s="69"/>
+      <c r="S37" s="62"/>
       <c r="T37" s="42"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
@@ -3109,16 +3163,16 @@
     </row>
     <row r="38" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="66"/>
-      <c r="C38" s="52"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="55"/>
       <c r="D38" s="12" t="s">
         <v>66</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F38" s="54"/>
-      <c r="G38" s="76"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="59"/>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
       <c r="J38" s="19"/>
@@ -3132,7 +3186,7 @@
       <c r="P38" s="19"/>
       <c r="Q38" s="19"/>
       <c r="R38" s="19"/>
-      <c r="S38" s="69"/>
+      <c r="S38" s="62"/>
       <c r="T38" s="15" t="s">
         <v>69</v>
       </c>
@@ -3144,30 +3198,32 @@
     </row>
     <row r="39" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="62"/>
-      <c r="C39" s="64"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="57"/>
       <c r="D39" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F39" s="55"/>
-      <c r="G39" s="77"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="60"/>
       <c r="H39" s="19"/>
       <c r="J39" s="19"/>
       <c r="K39" s="37"/>
       <c r="L39" s="19"/>
       <c r="M39" s="19"/>
       <c r="N39" s="19"/>
-      <c r="O39" s="85"/>
+      <c r="O39" s="51"/>
       <c r="P39" s="6" t="s">
         <v>11</v>
       </c>
       <c r="Q39" s="19"/>
       <c r="R39" s="19"/>
       <c r="S39" s="63"/>
-      <c r="T39" s="15"/>
+      <c r="T39" s="86" t="s">
+        <v>75</v>
+      </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
@@ -9542,12 +9598,6 @@
     <row r="1005" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B25:C30"/>
-    <mergeCell ref="G25:G30"/>
-    <mergeCell ref="S8:S39"/>
-    <mergeCell ref="G8:G19"/>
-    <mergeCell ref="G31:G39"/>
-    <mergeCell ref="B20:C24"/>
     <mergeCell ref="T5:T7"/>
     <mergeCell ref="F31:F39"/>
     <mergeCell ref="M5:P5"/>
@@ -9564,6 +9614,12 @@
     <mergeCell ref="Q5:S5"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="B8:C19"/>
+    <mergeCell ref="B25:C30"/>
+    <mergeCell ref="G25:G30"/>
+    <mergeCell ref="S8:S39"/>
+    <mergeCell ref="G8:G19"/>
+    <mergeCell ref="G31:G39"/>
+    <mergeCell ref="B20:C24"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/docs/상세개발계획서 AI담당.xlsx
+++ b/docs/상세개발계획서 AI담당.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sungjonghyun/3-1/산학프로젝트/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3603AAAC-8FAD-6D4B-A771-40D8884EBB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F8661A-7944-D24D-9D1C-55B639471573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="88">
   <si>
     <t>3팀 [21의 4분의 3 조] 상세개발계획서</t>
   </si>
@@ -5832,47 +5832,12 @@
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="22"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>개발</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="22"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="22"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이력</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6046,21 +6011,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -7300,28 +7250,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7343,9 +7276,12 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7356,17 +7292,31 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -7382,55 +7332,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>389192</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>228829</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>84667</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D24A982-C88A-309A-B300-E026F4FCCB1E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21386525" y="3048000"/>
-          <a:ext cx="13386304" cy="11938000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7678,26 +7579,26 @@
     </row>
     <row r="2" spans="1:30" ht="42.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="100"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
+      <c r="Q2" s="90"/>
+      <c r="R2" s="90"/>
+      <c r="S2" s="91"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -7708,24 +7609,24 @@
     </row>
     <row r="3" spans="1:30" ht="42.75" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="101"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="102"/>
-      <c r="S3" s="103"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+      <c r="R3" s="93"/>
+      <c r="S3" s="94"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -7736,24 +7637,24 @@
     </row>
     <row r="4" spans="1:30" ht="16.5" customHeight="1" thickBot="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="106"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="107"/>
-      <c r="M4" s="107"/>
-      <c r="N4" s="107"/>
-      <c r="O4" s="107"/>
-      <c r="P4" s="107"/>
-      <c r="Q4" s="107"/>
-      <c r="R4" s="107"/>
-      <c r="S4" s="107"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="101"/>
+      <c r="S4" s="101"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -7764,14 +7665,14 @@
     </row>
     <row r="5" spans="1:30" ht="29.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="109" t="s">
+      <c r="B5" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="81"/>
-      <c r="D5" s="109" t="s">
+      <c r="C5" s="96"/>
+      <c r="D5" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="105" t="s">
+      <c r="E5" s="98" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="7" t="s">
@@ -7780,25 +7681,25 @@
       <c r="G5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="110" t="s">
+      <c r="H5" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="112"/>
-      <c r="M5" s="95" t="s">
+      <c r="I5" s="106"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="106"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="96"/>
-      <c r="O5" s="96"/>
-      <c r="P5" s="97"/>
-      <c r="Q5" s="95" t="s">
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
+      <c r="P5" s="88"/>
+      <c r="Q5" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="R5" s="96"/>
-      <c r="S5" s="97"/>
-      <c r="T5" s="91" t="s">
+      <c r="R5" s="87"/>
+      <c r="S5" s="88"/>
+      <c r="T5" s="81" t="s">
         <v>3</v>
       </c>
       <c r="U5" s="1"/>
@@ -7810,10 +7711,10 @@
     </row>
     <row r="6" spans="1:30" ht="29.25" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="82"/>
+      <c r="B6" s="97"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="97"/>
       <c r="F6" s="9" t="s">
         <v>16</v>
       </c>
@@ -7856,7 +7757,7 @@
       <c r="S6" s="14">
         <v>17</v>
       </c>
-      <c r="T6" s="83"/>
+      <c r="T6" s="82"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
@@ -7871,10 +7772,10 @@
     </row>
     <row r="7" spans="1:30" ht="29.25" customHeight="1" thickBot="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="84"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="99"/>
       <c r="F7" s="15" t="s">
         <v>17</v>
       </c>
@@ -7917,7 +7818,7 @@
       <c r="S7" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="T7" s="83"/>
+      <c r="T7" s="82"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -7930,18 +7831,18 @@
     </row>
     <row r="8" spans="1:30" ht="29.25" customHeight="1" thickBot="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="115" t="s">
+      <c r="B8" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="81"/>
+      <c r="C8" s="96"/>
       <c r="D8" s="41" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="108"/>
-      <c r="G8" s="89"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="108"/>
       <c r="H8" s="73" t="s">
         <v>34</v>
       </c>
@@ -7965,16 +7866,16 @@
     </row>
     <row r="9" spans="1:30" ht="29.25" customHeight="1" thickBot="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="83"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="82"/>
       <c r="D9" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E9" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="93"/>
-      <c r="G9" s="87"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="109"/>
       <c r="H9" s="73" t="s">
         <v>34</v>
       </c>
@@ -7992,9 +7893,7 @@
       <c r="T9" s="33"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
-      <c r="W9" s="116" t="s">
-        <v>88</v>
-      </c>
+      <c r="W9" s="80"/>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
@@ -8002,16 +7901,16 @@
     </row>
     <row r="10" spans="1:30" ht="29.25" customHeight="1" thickBot="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="83"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="82"/>
       <c r="D10" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E10" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="93"/>
-      <c r="G10" s="87"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="109"/>
       <c r="H10" s="73" t="s">
         <v>34</v>
       </c>
@@ -8036,16 +7935,16 @@
     </row>
     <row r="11" spans="1:30" ht="29.25" customHeight="1" thickBot="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="83"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="82"/>
       <c r="D11" s="33" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="93"/>
-      <c r="G11" s="87"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="109"/>
       <c r="H11" s="74"/>
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
@@ -8071,16 +7970,16 @@
     </row>
     <row r="12" spans="1:30" ht="29.25" customHeight="1" thickBot="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="83"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="82"/>
       <c r="D12" s="33" t="s">
         <v>39</v>
       </c>
       <c r="E12" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="93"/>
-      <c r="G12" s="87"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="109"/>
       <c r="H12" s="74"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
@@ -8106,16 +8005,16 @@
     </row>
     <row r="13" spans="1:30" ht="29.25" customHeight="1" thickBot="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="83"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="82"/>
       <c r="D13" s="33" t="s">
         <v>40</v>
       </c>
       <c r="E13" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="93"/>
-      <c r="G13" s="87"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="109"/>
       <c r="H13" s="74"/>
       <c r="I13" s="29" t="s">
         <v>34</v>
@@ -8151,16 +8050,16 @@
     </row>
     <row r="14" spans="1:30" ht="29.25" customHeight="1" thickBot="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="82"/>
-      <c r="C14" s="83"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="82"/>
       <c r="D14" s="33" t="s">
         <v>41</v>
       </c>
       <c r="E14" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="93"/>
-      <c r="G14" s="87"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="109"/>
       <c r="H14" s="74"/>
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
@@ -8184,16 +8083,16 @@
     </row>
     <row r="15" spans="1:30" ht="29.25" customHeight="1" thickBot="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="82"/>
-      <c r="C15" s="83"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="82"/>
       <c r="D15" s="33" t="s">
         <v>42</v>
       </c>
       <c r="E15" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="93"/>
-      <c r="G15" s="87"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="109"/>
       <c r="H15" s="74"/>
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
@@ -8221,16 +8120,16 @@
     </row>
     <row r="16" spans="1:30" ht="29.25" customHeight="1" thickBot="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="83"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="82"/>
       <c r="D16" s="33" t="s">
         <v>43</v>
       </c>
       <c r="E16" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="93"/>
-      <c r="G16" s="87"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="109"/>
       <c r="H16" s="74"/>
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
@@ -8256,16 +8155,16 @@
     </row>
     <row r="17" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="82"/>
-      <c r="C17" s="83"/>
+      <c r="B17" s="97"/>
+      <c r="C17" s="82"/>
       <c r="D17" s="33" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="93"/>
-      <c r="G17" s="87"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="109"/>
       <c r="H17" s="74"/>
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
@@ -8291,16 +8190,16 @@
     </row>
     <row r="18" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="82"/>
-      <c r="C18" s="83"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="82"/>
       <c r="D18" s="33" t="s">
         <v>47</v>
       </c>
       <c r="E18" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="93"/>
-      <c r="G18" s="87"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="109"/>
       <c r="H18" s="74"/>
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
@@ -8326,16 +8225,16 @@
     </row>
     <row r="19" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="82"/>
-      <c r="C19" s="83"/>
+      <c r="B19" s="97"/>
+      <c r="C19" s="82"/>
       <c r="D19" s="33" t="s">
         <v>49</v>
       </c>
       <c r="E19" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="93"/>
-      <c r="G19" s="87"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="109"/>
       <c r="H19" s="74"/>
       <c r="I19" s="31"/>
       <c r="J19" s="31"/>
@@ -8361,16 +8260,16 @@
     </row>
     <row r="20" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="83"/>
+      <c r="B20" s="97"/>
+      <c r="C20" s="82"/>
       <c r="D20" s="33" t="s">
         <v>51</v>
       </c>
       <c r="E20" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="93"/>
-      <c r="G20" s="87"/>
+      <c r="F20" s="84"/>
+      <c r="G20" s="109"/>
       <c r="H20" s="74"/>
       <c r="I20" s="31"/>
       <c r="J20" s="31"/>
@@ -8396,16 +8295,16 @@
     </row>
     <row r="21" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="82"/>
-      <c r="C21" s="83"/>
+      <c r="B21" s="97"/>
+      <c r="C21" s="82"/>
       <c r="D21" s="33" t="s">
         <v>53</v>
       </c>
       <c r="E21" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="93"/>
-      <c r="G21" s="87"/>
+      <c r="F21" s="84"/>
+      <c r="G21" s="109"/>
       <c r="H21" s="74"/>
       <c r="I21" s="31"/>
       <c r="J21" s="31"/>
@@ -8433,16 +8332,16 @@
     </row>
     <row r="22" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="84"/>
-      <c r="C22" s="85"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="104"/>
       <c r="D22" s="44" t="s">
         <v>81</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="94"/>
-      <c r="G22" s="88"/>
+      <c r="F22" s="85"/>
+      <c r="G22" s="110"/>
       <c r="H22" s="75"/>
       <c r="I22" s="59"/>
       <c r="J22" s="59"/>
@@ -8468,18 +8367,18 @@
     </row>
     <row r="23" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="90" t="s">
+      <c r="B23" s="116" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="81"/>
+      <c r="C23" s="96"/>
       <c r="D23" s="41" t="s">
         <v>55</v>
       </c>
       <c r="E23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="108"/>
-      <c r="G23" s="89"/>
+      <c r="F23" s="102"/>
+      <c r="G23" s="108"/>
       <c r="H23" s="76"/>
       <c r="I23" s="29" t="s">
         <v>34</v>
@@ -8503,16 +8402,16 @@
     </row>
     <row r="24" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="82"/>
-      <c r="C24" s="83"/>
+      <c r="B24" s="97"/>
+      <c r="C24" s="82"/>
       <c r="D24" s="33" t="s">
         <v>56</v>
       </c>
       <c r="E24" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="93"/>
-      <c r="G24" s="87"/>
+      <c r="F24" s="84"/>
+      <c r="G24" s="109"/>
       <c r="H24" s="74"/>
       <c r="I24" s="35"/>
       <c r="J24" s="29" t="s">
@@ -8536,16 +8435,16 @@
     </row>
     <row r="25" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="82"/>
-      <c r="C25" s="83"/>
+      <c r="B25" s="97"/>
+      <c r="C25" s="82"/>
       <c r="D25" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E25" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="93"/>
-      <c r="G25" s="87"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="109"/>
       <c r="H25" s="74"/>
       <c r="I25" s="39"/>
       <c r="J25" s="36" t="s">
@@ -8569,16 +8468,16 @@
     </row>
     <row r="26" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="82"/>
-      <c r="C26" s="83"/>
+      <c r="B26" s="97"/>
+      <c r="C26" s="82"/>
       <c r="D26" s="33" t="s">
         <v>58</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F26" s="93"/>
-      <c r="G26" s="87"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="109"/>
       <c r="H26" s="74"/>
       <c r="I26" s="31"/>
       <c r="J26" s="36" t="s">
@@ -8602,16 +8501,16 @@
     </row>
     <row r="27" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="82"/>
-      <c r="C27" s="83"/>
+      <c r="B27" s="97"/>
+      <c r="C27" s="82"/>
       <c r="D27" s="33" t="s">
         <v>59</v>
       </c>
       <c r="E27" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="93"/>
-      <c r="G27" s="87"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="109"/>
       <c r="H27" s="74"/>
       <c r="I27" s="31"/>
       <c r="J27" s="30"/>
@@ -8637,16 +8536,16 @@
     </row>
     <row r="28" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="84"/>
-      <c r="C28" s="85"/>
+      <c r="B28" s="99"/>
+      <c r="C28" s="104"/>
       <c r="D28" s="44" t="s">
         <v>86</v>
       </c>
       <c r="E28" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="94"/>
-      <c r="G28" s="88"/>
+      <c r="F28" s="85"/>
+      <c r="G28" s="110"/>
       <c r="H28" s="77"/>
       <c r="I28" s="51"/>
       <c r="J28" s="51"/>
@@ -8670,18 +8569,18 @@
     </row>
     <row r="29" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="80" t="s">
+      <c r="B29" s="114" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="81"/>
+      <c r="C29" s="96"/>
       <c r="D29" s="41" t="s">
         <v>61</v>
       </c>
       <c r="E29" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="92"/>
-      <c r="G29" s="86"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="115"/>
       <c r="H29" s="78"/>
       <c r="I29" s="64" t="s">
         <v>34</v>
@@ -8707,16 +8606,16 @@
     </row>
     <row r="30" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="82"/>
-      <c r="C30" s="83"/>
+      <c r="B30" s="97"/>
+      <c r="C30" s="82"/>
       <c r="D30" s="33" t="s">
         <v>63</v>
       </c>
       <c r="E30" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="93"/>
-      <c r="G30" s="87"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="109"/>
       <c r="H30" s="74"/>
       <c r="I30" s="31"/>
       <c r="J30" s="34"/>
@@ -8740,16 +8639,16 @@
     </row>
     <row r="31" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="82"/>
-      <c r="C31" s="83"/>
+      <c r="B31" s="97"/>
+      <c r="C31" s="82"/>
       <c r="D31" s="33" t="s">
         <v>64</v>
       </c>
       <c r="E31" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F31" s="93"/>
-      <c r="G31" s="87"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="109"/>
       <c r="H31" s="74"/>
       <c r="I31" s="31"/>
       <c r="J31" s="31"/>
@@ -8771,16 +8670,16 @@
     </row>
     <row r="32" spans="1:25" ht="29.25" customHeight="1" thickBot="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="83"/>
+      <c r="B32" s="97"/>
+      <c r="C32" s="82"/>
       <c r="D32" s="33" t="s">
         <v>65</v>
       </c>
       <c r="E32" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F32" s="93"/>
-      <c r="G32" s="87"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="109"/>
       <c r="H32" s="74"/>
       <c r="I32" s="31"/>
       <c r="J32" s="31"/>
@@ -8804,16 +8703,16 @@
     </row>
     <row r="33" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="83"/>
+      <c r="B33" s="97"/>
+      <c r="C33" s="82"/>
       <c r="D33" s="33" t="s">
         <v>59</v>
       </c>
       <c r="E33" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="F33" s="93"/>
-      <c r="G33" s="87"/>
+      <c r="F33" s="84"/>
+      <c r="G33" s="109"/>
       <c r="H33" s="74"/>
       <c r="I33" s="31"/>
       <c r="J33" s="31"/>
@@ -8837,16 +8736,16 @@
     </row>
     <row r="34" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="83"/>
+      <c r="B34" s="97"/>
+      <c r="C34" s="82"/>
       <c r="D34" s="33" t="s">
         <v>67</v>
       </c>
       <c r="E34" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="F34" s="93"/>
-      <c r="G34" s="87"/>
+      <c r="F34" s="84"/>
+      <c r="G34" s="109"/>
       <c r="H34" s="74"/>
       <c r="I34" s="31"/>
       <c r="J34" s="72"/>
@@ -8872,16 +8771,16 @@
     </row>
     <row r="35" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="85"/>
+      <c r="B35" s="99"/>
+      <c r="C35" s="104"/>
       <c r="D35" s="44" t="s">
         <v>87</v>
       </c>
       <c r="E35" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="94"/>
-      <c r="G35" s="88"/>
+      <c r="F35" s="85"/>
+      <c r="G35" s="110"/>
       <c r="H35" s="75"/>
       <c r="I35" s="70"/>
       <c r="J35" s="68"/>
@@ -8907,18 +8806,18 @@
     </row>
     <row r="36" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="104" t="s">
+      <c r="B36" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="81"/>
+      <c r="C36" s="96"/>
       <c r="D36" s="41" t="s">
         <v>70</v>
       </c>
       <c r="E36" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F36" s="92"/>
-      <c r="G36" s="86"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="115"/>
       <c r="H36" s="79"/>
       <c r="I36" s="32"/>
       <c r="J36" s="32"/>
@@ -8944,16 +8843,16 @@
     </row>
     <row r="37" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="82"/>
-      <c r="C37" s="83"/>
+      <c r="B37" s="97"/>
+      <c r="C37" s="82"/>
       <c r="D37" s="33" t="s">
         <v>71</v>
       </c>
       <c r="E37" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="93"/>
-      <c r="G37" s="87"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="109"/>
       <c r="H37" s="74"/>
       <c r="I37" s="31"/>
       <c r="J37" s="30"/>
@@ -8977,16 +8876,16 @@
     </row>
     <row r="38" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="82"/>
-      <c r="C38" s="83"/>
+      <c r="B38" s="97"/>
+      <c r="C38" s="82"/>
       <c r="D38" s="33" t="s">
         <v>72</v>
       </c>
       <c r="E38" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F38" s="93"/>
-      <c r="G38" s="87"/>
+      <c r="F38" s="84"/>
+      <c r="G38" s="109"/>
       <c r="H38" s="74"/>
       <c r="I38" s="31"/>
       <c r="J38" s="31"/>
@@ -9010,16 +8909,16 @@
     </row>
     <row r="39" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="82"/>
-      <c r="C39" s="83"/>
+      <c r="B39" s="97"/>
+      <c r="C39" s="82"/>
       <c r="D39" s="33" t="s">
         <v>73</v>
       </c>
       <c r="E39" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F39" s="93"/>
-      <c r="G39" s="87"/>
+      <c r="F39" s="84"/>
+      <c r="G39" s="109"/>
       <c r="H39" s="74"/>
       <c r="I39" s="31"/>
       <c r="J39" s="31"/>
@@ -9043,16 +8942,16 @@
     </row>
     <row r="40" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="82"/>
-      <c r="C40" s="83"/>
+      <c r="B40" s="97"/>
+      <c r="C40" s="82"/>
       <c r="D40" s="33" t="s">
         <v>74</v>
       </c>
       <c r="E40" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="93"/>
-      <c r="G40" s="87"/>
+      <c r="F40" s="84"/>
+      <c r="G40" s="109"/>
       <c r="H40" s="74"/>
       <c r="I40" s="31"/>
       <c r="J40" s="31"/>
@@ -9076,16 +8975,16 @@
     </row>
     <row r="41" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="82"/>
-      <c r="C41" s="83"/>
+      <c r="B41" s="97"/>
+      <c r="C41" s="82"/>
       <c r="D41" s="33" t="s">
         <v>75</v>
       </c>
       <c r="E41" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F41" s="93"/>
-      <c r="G41" s="87"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="109"/>
       <c r="H41" s="74"/>
       <c r="I41" s="31"/>
       <c r="J41" s="31"/>
@@ -9109,16 +9008,16 @@
     </row>
     <row r="42" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="82"/>
-      <c r="C42" s="83"/>
+      <c r="B42" s="97"/>
+      <c r="C42" s="82"/>
       <c r="D42" s="33" t="s">
         <v>76</v>
       </c>
       <c r="E42" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="93"/>
-      <c r="G42" s="87"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="109"/>
       <c r="H42" s="74"/>
       <c r="I42" s="31"/>
       <c r="J42" s="31"/>
@@ -9142,16 +9041,16 @@
     </row>
     <row r="43" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="82"/>
-      <c r="C43" s="83"/>
+      <c r="B43" s="97"/>
+      <c r="C43" s="82"/>
       <c r="D43" s="33" t="s">
         <v>77</v>
       </c>
       <c r="E43" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F43" s="93"/>
-      <c r="G43" s="87"/>
+      <c r="F43" s="84"/>
+      <c r="G43" s="109"/>
       <c r="H43" s="74"/>
       <c r="I43" s="31"/>
       <c r="J43" s="31"/>
@@ -9177,16 +9076,16 @@
     </row>
     <row r="44" spans="1:26" ht="29.25" customHeight="1" thickBot="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="82"/>
-      <c r="C44" s="83"/>
+      <c r="B44" s="97"/>
+      <c r="C44" s="82"/>
       <c r="D44" s="50" t="s">
         <v>79</v>
       </c>
       <c r="E44" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F44" s="94"/>
-      <c r="G44" s="88"/>
+      <c r="F44" s="85"/>
+      <c r="G44" s="110"/>
       <c r="H44" s="77"/>
       <c r="I44" s="34"/>
       <c r="J44" s="51"/>
@@ -15561,6 +15460,11 @@
     <row r="1010" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B29:C35"/>
+    <mergeCell ref="G29:G35"/>
+    <mergeCell ref="G8:G22"/>
+    <mergeCell ref="G36:G44"/>
+    <mergeCell ref="B23:C28"/>
     <mergeCell ref="T5:T7"/>
     <mergeCell ref="F36:F44"/>
     <mergeCell ref="M5:P5"/>
@@ -15577,15 +15481,9 @@
     <mergeCell ref="Q5:S5"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="B8:C22"/>
-    <mergeCell ref="B29:C35"/>
-    <mergeCell ref="G29:G35"/>
-    <mergeCell ref="G8:G22"/>
-    <mergeCell ref="G36:G44"/>
-    <mergeCell ref="B23:C28"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>